--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4611B262-A01C-4F3F-AFF0-4348B66944F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544B3E58-4C8D-41FF-9159-8AACCDF41AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -143,9 +143,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>双嵐の風雲龍王・ネフェル&amp;アネモスの希石,アネモスの剣の希石,ネフェルの盾の希石,ブルッカのおとも・べりドラの希石</t>
-  </si>
-  <si>
     <t>スーパ―ノエルドラゴン(×10),ニジピィ(×4),ぷれドラ(×2)</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -207,6 +204,32 @@
   </si>
   <si>
     <t>れもドラ(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風雲の龍王</t>
+    <rPh sb="0" eb="2">
+      <t>フウウン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リュウオウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>双嵐の風雲龍王・ネフェル&amp;アネモスの希石(ボス本体),アネモスの剣の希石(ボス部位),ネフェルの盾の希石(ボス部位),ブルッカのおとも・べりドラの希石(乱入部位)</t>
+    <rPh sb="23" eb="25">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="76" eb="80">
+      <t>ランニュウブイ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1288,19 +1311,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1">
         <v>99</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1314,16 +1337,16 @@
         <v>99</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1337,16 +1360,16 @@
         <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544B3E58-4C8D-41FF-9159-8AACCDF41AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEC2CC1-262F-45EA-B824-8AFD17BE2CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -93,10 +93,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>キングゴールドドラゴンズ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>確定ランダムドロップ</t>
     <rPh sb="0" eb="2">
       <t>カクテイ</t>
@@ -230,6 +226,10 @@
     <rPh sb="76" eb="80">
       <t>ランニュウブイ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キングゴールドドラゴンズ(×1)</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1257,10 +1257,10 @@
         <v>11</v>
       </c>
       <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
         <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1277,10 +1277,10 @@
         <v>5</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1294,16 +1294,16 @@
         <v>99</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1311,19 +1311,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>99</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1337,16 +1337,16 @@
         <v>99</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1360,16 +1360,16 @@
         <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEC2CC1-262F-45EA-B824-8AFD17BE2CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFF10FC-AA3A-42E5-93BD-163CE71A923C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -230,6 +243,77 @@
   </si>
   <si>
     <t>キングゴールドドラゴンズ(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>経験値</t>
+    <rPh sb="0" eb="3">
+      <t>ケイケンチ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1億</t>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.5億</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.6億</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ポイント</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コイン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>30億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>40億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>42億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>経験値ストック</t>
+    <rPh sb="0" eb="3">
+      <t>ケイケンチ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>プラス限界突破</t>
+    <rPh sb="3" eb="7">
+      <t>ゲンカイトッパ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -829,7 +913,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,6 +933,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1225,19 +1312,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="18.58203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.58203125" customWidth="1"/>
-    <col min="4" max="4" width="162.1640625" customWidth="1"/>
-    <col min="5" max="5" width="87.6640625" customWidth="1"/>
-    <col min="6" max="6" width="61.6640625" customWidth="1"/>
-    <col min="7" max="7" width="255.5" customWidth="1"/>
-    <col min="8" max="8" width="25.58203125" customWidth="1"/>
+    <col min="4" max="8" width="25.58203125" customWidth="1"/>
+    <col min="9" max="9" width="162.1640625" customWidth="1"/>
+    <col min="10" max="10" width="87.6640625" customWidth="1"/>
+    <col min="11" max="11" width="61.6640625" customWidth="1"/>
+    <col min="12" max="12" width="255.5" customWidth="1"/>
+    <col min="13" max="13" width="25.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1248,22 +1336,37 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1273,17 +1376,30 @@
       <c r="C2" s="1">
         <v>99</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2970</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1293,20 +1409,33 @@
       <c r="C3" s="1">
         <v>99</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2970</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1316,17 +1445,30 @@
       <c r="C4" s="1">
         <v>99</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2970</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1336,20 +1478,33 @@
       <c r="C5" s="1">
         <v>99</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="6">
+        <v>6666</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -1359,16 +1514,31 @@
       <c r="C6" s="1">
         <v>99</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2970</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="6">
+        <v>30</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>28</v>
       </c>
     </row>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFF10FC-AA3A-42E5-93BD-163CE71A923C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F14582-7D9D-47FC-BA7C-A240EF37E16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -176,14 +176,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>潜在たまドラ☆スキル遅延耐性(×10～11),潜在たまドラ☆防御力無視(×1)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>潜在たまドラ☆属性吸収貫通,潜在たまドラ☆スキルブースト++,潜在たまドラ☆アシスト無効回復,潜在たまドラ☆ダメージ上限解放(×7～8)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>ぶどドラ(×1)</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -204,10 +196,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ニジピィ(×4～5),潜在たまドラ☆スキル遅延耐性(×3)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×3)</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -314,6 +302,75 @@
     <rPh sb="3" eb="7">
       <t>ゲンカイトッパ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>注意書き</t>
+    <rPh sb="0" eb="3">
+      <t>チュウイガ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※乱入が5Fのとき：遅延耐性潜在は10個、6枠潜在は8個 / 乱入が6Fのとき：遅延耐性潜在は11個、6枠潜在は7個</t>
+    <rPh sb="1" eb="3">
+      <t>ランニュウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>チエンタイセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ワクセンザイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ランニュウ</t>
+    </rPh>
+    <rPh sb="40" eb="46">
+      <t>チエンタイセイセンザイ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>ワクセンザイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※乱入本体でニジピィがドロップするが、一定確率でドロップする。</t>
+    <rPh sb="1" eb="3">
+      <t>ランニュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>イッテイカクリツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆スキル遅延耐性(×10～11(※)),潜在たまドラ☆防御力無視(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆属性吸収貫通,潜在たまドラ☆スキルブースト++,潜在たまドラ☆アシスト無効回復,潜在たまドラ☆ダメージ上限解放(×7～8(※))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ニジピィ(×4～5(※)),潜在たまドラ☆スキル遅延耐性(×3)</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1312,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="18.58203125" style="2" customWidth="1"/>
@@ -1323,9 +1380,10 @@
     <col min="11" max="11" width="61.6640625" customWidth="1"/>
     <col min="12" max="12" width="255.5" customWidth="1"/>
     <col min="13" max="13" width="25.58203125" customWidth="1"/>
+    <col min="14" max="14" width="104.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1336,19 +1394,19 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
@@ -1365,8 +1423,11 @@
       <c r="M1" t="s">
         <v>14</v>
       </c>
+      <c r="N1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1377,29 +1438,29 @@
         <v>99</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F2" s="6">
         <v>2970</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1410,16 +1471,16 @@
         <v>99</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F3" s="6">
         <v>2970</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="4" t="s">
@@ -1435,31 +1496,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
         <v>99</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F4" s="6">
         <v>2970</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>20</v>
@@ -1468,7 +1529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1479,32 +1540,35 @@
         <v>99</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6">
         <v>6666</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="L5" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -1515,31 +1579,34 @@
         <v>99</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F6" s="6">
         <v>2970</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H6" s="6">
         <v>30</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="L6" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F14582-7D9D-47FC-BA7C-A240EF37E16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC14A1A-5194-41DD-9BCE-70ED62EC897E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
+    <sheet name="素材名と図鑑番号の対応" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="81">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -371,6 +372,268 @@
   </si>
   <si>
     <t>ニジピィ(×4～5(※)),潜在たまドラ☆スキル遅延耐性(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>バトル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>図鑑No</t>
+    <rPh sb="0" eb="2">
+      <t>ズカン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>素材名</t>
+    <rPh sb="0" eb="3">
+      <t>ソザイメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆HP強化++</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆攻撃強化++</t>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆回復強化++</t>
+    <rPh sb="7" eb="9">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆火ダメージ軽減+</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ケイゲン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆水ダメージ軽減+</t>
+    <rPh sb="7" eb="8">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆木ダメージ軽減+</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆光ダメージ軽減+</t>
+    <rPh sb="7" eb="8">
+      <t>ヒカリ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆闇ダメージ軽減+</t>
+    <rPh sb="7" eb="8">
+      <t>ヤミ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キングゴールドドラゴンズ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆枠解放</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>創装の宝玉</t>
+    <rPh sb="0" eb="1">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウギョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ダイヤドラゴンフルーツ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>古代の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>三神面</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>3</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>メン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゴールドたまドラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ニジピィ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ぷれドラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>べりドラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆スキル遅延耐性</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>チエンタイセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆防御力無視</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆属性吸収貫通</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ゾクセイキュウシュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンツウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆スキルブースト++</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆アシスト無効回復</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ムコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆ダメージ上限解放</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ジョウゲンカイホウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ぶどドラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングルビードラゴン</t>
+    <rPh sb="0" eb="1">
+      <t>ゴク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングサファイアドラゴン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングエメラルドドラゴン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングゴールドドラゴン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングメタルドラゴン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>れもドラ</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -378,7 +641,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,6 +801,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -970,7 +1240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -993,6 +1263,9 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1369,21 +1642,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="18.58203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.58203125" customWidth="1"/>
-    <col min="4" max="8" width="25.58203125" customWidth="1"/>
-    <col min="9" max="9" width="162.1640625" customWidth="1"/>
-    <col min="10" max="10" width="87.6640625" customWidth="1"/>
-    <col min="11" max="11" width="61.6640625" customWidth="1"/>
-    <col min="12" max="12" width="255.5" customWidth="1"/>
-    <col min="13" max="13" width="25.58203125" customWidth="1"/>
-    <col min="14" max="14" width="104.1640625" customWidth="1"/>
+    <col min="3" max="4" width="10.58203125" customWidth="1"/>
+    <col min="5" max="9" width="25.58203125" customWidth="1"/>
+    <col min="10" max="10" width="162.1640625" customWidth="1"/>
+    <col min="11" max="11" width="87.6640625" customWidth="1"/>
+    <col min="12" max="12" width="61.6640625" customWidth="1"/>
+    <col min="13" max="13" width="255.5" customWidth="1"/>
+    <col min="14" max="14" width="25.58203125" customWidth="1"/>
+    <col min="15" max="15" width="104.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1394,40 +1667,43 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>39</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1437,30 +1713,33 @@
       <c r="C2" s="1">
         <v>99</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="1">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="6">
         <v>2970</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="6"/>
+      <c r="J2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1470,33 +1749,36 @@
       <c r="C3" s="1">
         <v>99</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="1">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="6">
         <v>2970</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1506,30 +1788,33 @@
       <c r="C4" s="1">
         <v>99</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="1">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <v>2970</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="6"/>
+      <c r="J4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1539,36 +1824,39 @@
       <c r="C5" s="1">
         <v>99</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="1">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <v>6666</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="6"/>
+      <c r="J5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="O5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -1578,34 +1866,37 @@
       <c r="C6" s="1">
         <v>99</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="1">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>2970</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <v>30</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1614,4 +1905,278 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="12.5" style="7" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="7">
+        <v>1077</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="7">
+        <v>1081</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="7">
+        <v>1083</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7">
+        <v>1709</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7">
+        <v>2250</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7">
+        <v>2425</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7">
+        <v>3795</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7">
+        <v>3891</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7">
+        <v>3911</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7">
+        <v>3971</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7">
+        <v>3973</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7">
+        <v>4369</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7">
+        <v>4370</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7">
+        <v>4371</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7">
+        <v>4372</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7">
+        <v>4373</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7">
+        <v>5739</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7">
+        <v>6077</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7">
+        <v>7020</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7">
+        <v>7021</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7">
+        <v>7022</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7">
+        <v>7023</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7">
+        <v>9000</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7">
+        <v>9454</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7">
+        <v>10022</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7">
+        <v>10023</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7">
+        <v>10024</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7">
+        <v>10025</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="7">
+        <v>10026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7">
+        <v>10114</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="7">
+        <v>13667</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B32">
+    <sortCondition ref="A2:A32"/>
+  </sortState>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC14A1A-5194-41DD-9BCE-70ED62EC897E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937A78F5-461E-446A-BE45-80759A145927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -634,6 +634,329 @@
   </si>
   <si>
     <t>れもドラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>宿木の大樹霊王・アドネアの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ヤド</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイジュ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>レイオウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>宿木の大樹霊王・アドネアの左根の希石</t>
+    <rPh sb="0" eb="1">
+      <t>ヤド</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイジュ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>レイオウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ネ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>宿木の大樹霊王・アドネアの右根の希石</t>
+    <rPh sb="0" eb="1">
+      <t>ヤド</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイジュ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>レイオウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ネ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>神器に宿る者・グラオルの希石</t>
+    <rPh sb="0" eb="1">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ウツワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヤド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火山の紅蓮機王・ヴォルガントの希石</t>
+    <rPh sb="0" eb="2">
+      <t>カザン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>グレン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キオウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ヴォルガントの槍の希石</t>
+    <rPh sb="7" eb="8">
+      <t>ヤリ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ヴォルガントの盾の希石</t>
+    <rPh sb="7" eb="8">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>神器に宿る者・ガリヴァンの希石</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>双嵐の風雲龍王・ネフェル&amp;アネモスの希石</t>
+    <rPh sb="0" eb="2">
+      <t>ソウアラシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フウウン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>リュウオウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アネモスの剣の希石</t>
+    <rPh sb="5" eb="6">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ネフェルの盾の希石</t>
+    <rPh sb="5" eb="6">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ブルッカのおとも・べりドラの希石</t>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>黒雲の霧雨魔王・グレゴウルの希石</t>
+    <rPh sb="0" eb="2">
+      <t>コクウン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キリサメ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>マオウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレゴウルの魔剣ミスティレインの希石</t>
+    <rPh sb="6" eb="8">
+      <t>マケン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレゴウルの翼の希石</t>
+    <rPh sb="6" eb="7">
+      <t>ツバサ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレーシスのおとも・ぶどドラの希石</t>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>虹耀の天穹神王・アレクセンの希石</t>
+    <rPh sb="0" eb="2">
+      <t>ニジヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ソラ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アレクセンの聖鳥の希石</t>
+    <rPh sb="6" eb="7">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トリ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アレクセンの翼の希石</t>
+    <rPh sb="6" eb="7">
+      <t>ツバサ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レモックのおとも・れもドラの希石</t>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1909,7 +2232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" customWidth="1"/>
@@ -2166,15 +2489,175 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="7">
+        <v>13499</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7">
+        <v>13500</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="7">
+        <v>13501</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7">
+        <v>13503</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="7">
+        <v>13590</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="7">
+        <v>13591</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7">
+        <v>13592</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7">
+        <v>13594</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="7">
         <v>13667</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>69</v>
       </c>
     </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7">
+        <v>13799</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="7">
+        <v>13800</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7">
+        <v>13801</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7">
+        <v>13803</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="7">
+        <v>13821</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="7">
+        <v>13822</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="7">
+        <v>13823</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="7">
+        <v>13825</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="7">
+        <v>14023</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="7">
+        <v>14024</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="7">
+        <v>14025</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="7">
+        <v>14027</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B32">
-    <sortCondition ref="A2:A32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B52">
+    <sortCondition ref="A2:A52"/>
   </sortState>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937A78F5-461E-446A-BE45-80759A145927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC338BE-02CD-4AC1-9A37-C0762273647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="107">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -956,6 +956,153 @@
     </rPh>
     <rPh sb="15" eb="16">
       <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>交換可能なレート</t>
+    <rPh sb="0" eb="4">
+      <t>コウカンカノウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅蓮機王・ヴォルガント：200周,ヴォルガントのヴォルカニックランス：99周,神器に宿る者・ガリヴァン：25周</t>
+    <rPh sb="0" eb="4">
+      <t>グレンキオウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カミウツワ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ヤド</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大樹霊王・アドネア：200周,アドネアの樹霊根：99周,神器に宿る者・グラオル：25周</t>
+    <rPh sb="0" eb="2">
+      <t>タイジュ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>レイオウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ジュ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ネ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジンギ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヤド</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風雲龍王・ネフェル&amp;アネモス：200周,アネモスの剣&amp;ネフェルの盾：99周,べりドラのカード：25周</t>
+    <rPh sb="0" eb="2">
+      <t>フウウン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リュウオウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>霧雨魔王・グレゴウル：200周,グレゴウルの魔剣ミスティレイン：99周,ぶどドラのカード：25周</t>
+    <rPh sb="0" eb="2">
+      <t>キリサメ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マオウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>マケン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>天穹神王・アレクセン：200周,アレクセンの王笏アトモスワンダー：99周,れもドラのカード：25周</t>
+    <rPh sb="0" eb="1">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ソラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>シャク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>シュウ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -1965,21 +2112,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="18.58203125" style="2" customWidth="1"/>
     <col min="3" max="4" width="10.58203125" customWidth="1"/>
-    <col min="5" max="9" width="25.58203125" customWidth="1"/>
-    <col min="10" max="10" width="162.1640625" customWidth="1"/>
-    <col min="11" max="11" width="87.6640625" customWidth="1"/>
-    <col min="12" max="12" width="61.6640625" customWidth="1"/>
-    <col min="13" max="13" width="255.5" customWidth="1"/>
-    <col min="14" max="14" width="25.58203125" customWidth="1"/>
-    <col min="15" max="15" width="104.1640625" customWidth="1"/>
+    <col min="5" max="5" width="108.75" customWidth="1"/>
+    <col min="6" max="10" width="25.58203125" customWidth="1"/>
+    <col min="11" max="11" width="162.1640625" customWidth="1"/>
+    <col min="12" max="12" width="87.6640625" customWidth="1"/>
+    <col min="13" max="13" width="61.6640625" customWidth="1"/>
+    <col min="14" max="14" width="255.5" customWidth="1"/>
+    <col min="15" max="15" width="25.58203125" customWidth="1"/>
+    <col min="16" max="16" width="104.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1993,40 +2141,43 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>40</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2040,29 +2191,32 @@
         <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="6">
+      <c r="H2" s="6">
         <v>2970</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2076,32 +2230,35 @@
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="6">
+      <c r="H3" s="6">
         <v>2970</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="6"/>
+      <c r="K3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -2115,29 +2272,32 @@
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>2970</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2151,35 +2311,38 @@
         <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="6">
         <v>6666</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="6"/>
+      <c r="K5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -2193,33 +2356,36 @@
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>2970</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6">
         <v>30</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>43</v>
       </c>
     </row>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC338BE-02CD-4AC1-9A37-C0762273647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0FE877-D45E-4F3D-96E5-6AF40D6D9A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="227">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -1104,6 +1104,1435 @@
     <rPh sb="48" eb="49">
       <t>シュウ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超重力</t>
+    <rPh sb="0" eb="3">
+      <t>チョウジュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超高度</t>
+    <rPh sb="0" eb="3">
+      <t>チョウコウド</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>その他の効果</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陽/陰</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陰</t>
+    <rPh sb="0" eb="1">
+      <t>イン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陽</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/3333</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【灼熱】,HP10%減少,回復力1/2</t>
+    <rPh sb="1" eb="3">
+      <t>シャクネツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>カイフクリョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/3500</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【深緑】,木属性の攻撃力と回復力が2倍,お邪魔ドロップ目覚め(解除不可)</t>
+    <rPh sb="1" eb="3">
+      <t>フカミドリ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>カイフクリョク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジャマ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>カイジョフカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/500</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/16</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/18</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/600</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/20</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>守霊の天体</t>
+    <rPh sb="0" eb="1">
+      <t>マモ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木星の守護者</t>
+    <rPh sb="0" eb="2">
+      <t>モクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シュゴシャ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守護者</t>
+    <rPh sb="0" eb="2">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シュゴシャ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金星の守護者</t>
+    <rPh sb="0" eb="2">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シュゴシャ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守護者</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シュゴシャ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守護者</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シュゴシャ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陰</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木星の守霊・ユーピリス：50周,ジュピトールのプラネットハンマー：50周,予見の魔神将・アスタロトのカード：25周</t>
+    <rPh sb="0" eb="2">
+      <t>モクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マモ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヨケン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>マジン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守霊・メルキス：99～100周,マーキュリアのプラネットランス：99～100周,義侠の魔神将・アモンのカード：25周</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>金星の守霊・ハクレイ：99～100周,タイハクセイの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>七星剣：99～100周,閃剣の魔神将・バアルのカード：25周</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>7</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>マジン</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守霊・メルナ：99～100周,セレナディアの双月棍：99～100周,逆心の神魔王・ルシファーのカード：25周</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュレイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フタツキ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツエ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ギャクシン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>マオウ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守霊・ソルディー：99～100周,サンドルムの烈火輪：99～100周,邪炎の魔神将・ベリアルのカード：25周</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュレイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジャエン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>マジン</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/2500</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/2</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/2000</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/4</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>6,500万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>25億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.5億</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>40億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.75億</t>
+    <rPh sb="4" eb="5">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>50億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>2億</t>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>55億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>3億</t>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>100億</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木星の守霊・ユーピリスの希石(ボス本体),木星の魔導神機・ジュピトールの希石(ボス部位),木星の希石(ボス部位),ソフィの召喚・アスタロトの希石(乱入部位)</t>
+    <rPh sb="0" eb="2">
+      <t>モクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュレイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モクセイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>モクセイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ショウカン</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ランニュウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ニジピィ(×4)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎魔刃・イグニスパーダ(×1),旋風龍・ガスティン(×1)</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤイバ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センプウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆HP強化+,潜在たまドラ☆攻撃強化+,潜在たまドラ☆回復強化+,潜在たまドラ☆全パラメータ強化(×2),潜在たまドラ☆HP強化+,潜在たまドラ☆攻撃強化+,潜在たまドラ☆回復強化+,潜在たまドラ☆全パラメータ強化,潜在たまドラ☆HP強化++,潜在たまドラ☆攻撃強化++,潜在たまドラ☆回復強化++(×8)</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>センザイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サゲピィ,とじたまドラ,モドリット(×1)</t>
+  </si>
+  <si>
+    <t>サゲピィ,とじたまドラ,モドリット(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木星の守霊・ユーピリスの希石</t>
+  </si>
+  <si>
+    <t>木星の魔導神機・ジュピトールの希石</t>
+  </si>
+  <si>
+    <t>木星の希石</t>
+  </si>
+  <si>
+    <t>ソフィの召喚・アスタロトの希石</t>
+  </si>
+  <si>
+    <t>潜在たまドラ☆HP強化+</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆攻撃強化+</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆回復強化+</t>
+    <rPh sb="7" eb="9">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆全パラメータ強化</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サゲピィ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>とじたまドラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>モドリット</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎魔刃・イグニスパーダ</t>
+    <rPh sb="0" eb="1">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤイバ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>旋風龍・ガスティン</t>
+    <rPh sb="0" eb="2">
+      <t>センプウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守霊・メルキスの希石</t>
+    <rPh sb="0" eb="2">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュレイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守護聖霊・マーキュリアの希石</t>
+    <rPh sb="0" eb="2">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュゴ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の希石</t>
+    <rPh sb="0" eb="2">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・アモンの希石</t>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マーキュリアのプラネットランスの希石</t>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守霊・メルキスの希石(ボス本体),水星の守護聖霊・マーキュリアの希石(ボス部位),水星の希石(ボス部位),マーキュリアのプラネットランスの希石(ボス部位),ソフィの召喚・アモンの希石(乱入部位)</t>
+    <rPh sb="16" eb="18">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="95" eb="99">
+      <t>ランニュウブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆スキル遅延耐性(×10),ニジピィ(×1)</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>チエンタイセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×2)</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風魔斧・アクスロン</t>
+    <rPh sb="0" eb="2">
+      <t>フウマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オノ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>青煌鬼・アウレア</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オニ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>青煌鬼・アウレア(×1),風魔斧・アクスロン(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金星の守霊・ハクレイの希石</t>
+    <rPh sb="0" eb="2">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュレイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金星の守護星獣・タイハクセイの希石</t>
+    <rPh sb="0" eb="2">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュゴ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ケモノ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金星の希石</t>
+    <rPh sb="0" eb="2">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>タイハクセイの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>七星剣の希石</t>
+    </r>
+    <rPh sb="7" eb="8">
+      <t>7</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・バアルの希石</t>
+    <rPh sb="4" eb="6">
+      <t>ショウカン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆リーダーチェンジ耐性</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆お邪魔目覚め耐性</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジャマ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆毒目覚め耐性</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ドク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆ダメージ無効貫通</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ムコウカンツウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆ダメージ吸収貫通</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>キュウシュウカンツウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆ルーレット回復</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆消せないドロップ回復</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆雲・操作不可回復</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>クモ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>ソウサフカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆ダメージ上限解放8倍</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ジョウゲンカイホウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆部位追撃</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツイゲキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>闇魔槍・デスピアード</t>
+    <rPh sb="0" eb="1">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤリ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>流星龍・メテオロン</t>
+    <rPh sb="0" eb="2">
+      <t>リュウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金星の守霊・ハクレイの希石(ボス本体),金星の守護星獣・タイハクセイの希石(ボス部位),金星の希石(ボス部位),タイハクセイの七星剣の希石(ボス部位),ソフィの召喚・バアルの希石(乱入部位)</t>
+    <rPh sb="16" eb="18">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="90" eb="94">
+      <t>ランニュウブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパ―ノエルドラゴン(×10)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>流星龍・メテオロン(×1),闇魔槍・デスピアード(×1),ダイヤドラゴンフルーツ(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆ダメージ吸収貫通,潜在たまドラ☆ルーレット回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆スキルブースト++,潜在たまドラ☆アシスト無効回復,潜在たまドラ☆部位追撃,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守霊・メレナの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュレイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守護妖魔・セレナディアの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨウマ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の希石</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・ルシファーの希石</t>
+    <rPh sb="4" eb="6">
+      <t>ショウカン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ホノピィ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミズピィ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>モクピィ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ヒカピィ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ヤミピィ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>輝眼杖・ワンドゥーム</t>
+    <rPh sb="0" eb="1">
+      <t>カガヤ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暗玉兎・デルムン</t>
+    <rPh sb="0" eb="1">
+      <t>クラ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウサギ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守霊・メレナの希石(ボス本体),月の守護妖魔・セレナディアの希石(ボス部位),月の希石(ボス部位),ソフィの召喚・ルシファーの希石(乱入部位)</t>
+    <rPh sb="14" eb="16">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="68" eb="72">
+      <t>ランニュウブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>創装の宝玉(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×10),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サゲピィ,とじたまドラ,モドリット,ゴールドたまドラ(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>輝眼杖・ワンドゥーム(×1),暗玉兎・デルムン(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守霊・ソルディーの希石</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュレイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守護星龍・サンドルムの希石</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュゴ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の希石</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サンドルムの烈火輪の希石</t>
+    <rPh sb="6" eb="7">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・ベリアルの希石</t>
+    <rPh sb="4" eb="6">
+      <t>ショウカン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼魔銃・デピストル</t>
+    <rPh sb="0" eb="1">
+      <t>アオイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅炎龍・ソルド―ラ</t>
+    <rPh sb="0" eb="1">
+      <t>ベニ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守霊・ソルディーの希石(ボス本体),太陽の守護星龍・サンドルムの希石(ボス部位),太陽の希石(ボス部位),サンドルムの烈火輪の希石(ボス部位),ソフィの召喚・ベリアルの希石(乱入部位)</t>
+    <rPh sb="17" eb="19">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="90" eb="94">
+      <t>ランニュウブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆スキルブースト++(×2),潜在たまドラ☆アシスト無効回復(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅炎龍・ソルド―ラ(×1),蒼魔銃・デピストル(×1),ゴールドたまドラ(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※基本、各色ピィ×1だが、確率でそれぞれニジピィに変化する。</t>
+    <rPh sb="1" eb="3">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクショク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>創装の宝玉,ダイヤドラゴンフルーツ,古代の三神面(×5),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ,ニジピィ(×5(※)),火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2～3)</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1466,7 +2895,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1581,8 +3010,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1709,36 +3188,76 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1771,6 +3290,7 @@
     <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="計算" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="警告文" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="桁区切り" xfId="42" builtinId="6"/>
     <cellStyle name="見出し 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="見出し 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="見出し 3" xfId="4" builtinId="18" customBuiltin="1"/>
@@ -2112,283 +3632,630 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="18.58203125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="10.58203125" customWidth="1"/>
-    <col min="5" max="5" width="108.75" customWidth="1"/>
-    <col min="6" max="10" width="25.58203125" customWidth="1"/>
-    <col min="11" max="11" width="162.1640625" customWidth="1"/>
-    <col min="12" max="12" width="87.6640625" customWidth="1"/>
-    <col min="13" max="13" width="61.6640625" customWidth="1"/>
-    <col min="14" max="14" width="255.5" customWidth="1"/>
-    <col min="15" max="15" width="25.58203125" customWidth="1"/>
-    <col min="16" max="16" width="104.1640625" customWidth="1"/>
+    <col min="3" max="4" width="10.58203125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="10.58203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="108.75" style="18" customWidth="1"/>
+    <col min="7" max="8" width="30.58203125" style="19" customWidth="1"/>
+    <col min="9" max="9" width="75.58203125" style="18" customWidth="1"/>
+    <col min="10" max="14" width="25.58203125" style="18" customWidth="1"/>
+    <col min="15" max="15" width="163.75" style="17" customWidth="1"/>
+    <col min="16" max="16" width="71.1640625" style="17" customWidth="1"/>
+    <col min="17" max="17" width="69.08203125" style="17" customWidth="1"/>
+    <col min="18" max="18" width="255.5" style="17" customWidth="1"/>
+    <col min="19" max="19" width="102.5" style="17" customWidth="1"/>
+    <col min="20" max="20" width="104.1640625" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="10">
         <v>99</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="10">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="L2" s="12">
         <v>2970</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="M2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="12"/>
+      <c r="O2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="P2" s="14"/>
+      <c r="Q2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="R2" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+    </row>
+    <row r="3" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="10">
         <v>99</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="10">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="K3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="6">
+      <c r="L3" s="12">
         <v>2970</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="M3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="4" t="s">
+      <c r="N3" s="12"/>
+      <c r="O3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="P3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="Q3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="R3" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+    </row>
+    <row r="4" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="10">
         <v>99</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="10">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="K4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="L4" s="12">
         <v>2970</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="M4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="4" t="s">
+      <c r="N4" s="12"/>
+      <c r="O4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="P4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="Q4" s="13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3" t="s">
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+    </row>
+    <row r="5" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="10">
         <v>99</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="10">
         <v>15</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="K5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="6">
+      <c r="L5" s="12">
         <v>6666</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="M5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="4" t="s">
+      <c r="N5" s="12"/>
+      <c r="O5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="P5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="Q5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="R5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="S5" s="14"/>
+      <c r="T5" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="10">
         <v>99</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="10">
         <v>15</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="K6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="6">
+      <c r="L6" s="12">
         <v>2970</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="M6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="6">
+      <c r="N6" s="12">
         <v>30</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="O6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="P6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="Q6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="R6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="S6" s="14"/>
+      <c r="T6" s="13" t="s">
         <v>43</v>
       </c>
     </row>
+    <row r="7" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="10">
+        <v>99</v>
+      </c>
+      <c r="D7" s="10">
+        <v>12</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="L7" s="12">
+        <v>2970</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="T7" s="14"/>
+    </row>
+    <row r="8" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="10">
+        <v>99</v>
+      </c>
+      <c r="D8" s="10">
+        <v>13</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="L8" s="12">
+        <v>2970</v>
+      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="T8" s="14"/>
+    </row>
+    <row r="9" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="10">
+        <v>99</v>
+      </c>
+      <c r="D9" s="10">
+        <v>13</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" s="12">
+        <v>7777</v>
+      </c>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+    </row>
+    <row r="10" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="10">
+        <v>99</v>
+      </c>
+      <c r="D10" s="10">
+        <v>14</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="L10" s="12">
+        <v>5000</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="S10" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="T10" s="14"/>
+    </row>
+    <row r="11" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="10">
+        <v>99</v>
+      </c>
+      <c r="D11" s="10">
+        <v>15</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="L11" s="12">
+        <v>9999</v>
+      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="S11" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="T11" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="13" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="14" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="15" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="16" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="17" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="18" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="19" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2398,11 +4265,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="7" customWidth="1"/>
-    <col min="2" max="2" width="43.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -2414,411 +4281,851 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="7">
+      <c r="A2" s="3">
         <v>1077</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="7">
+      <c r="A3" s="3">
         <v>1081</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7">
+      <c r="A4" s="3">
         <v>1083</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>1709</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7">
+      <c r="A6" s="3">
         <v>2250</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>2425</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7">
+      <c r="A8" s="3">
         <v>3795</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7">
+      <c r="A9" s="3">
         <v>3891</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7">
+      <c r="A10" s="3">
         <v>3911</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7">
+      <c r="A11" s="3">
         <v>3971</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7">
+      <c r="A12" s="3">
         <v>3973</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7">
+      <c r="A13" s="3">
         <v>4369</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7">
+      <c r="A14" s="3">
         <v>4370</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="7">
+      <c r="A15" s="3">
         <v>4371</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7">
+      <c r="A16" s="3">
         <v>4372</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7">
+      <c r="A17" s="3">
         <v>4373</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="7">
+      <c r="A18" s="3">
         <v>5739</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="7">
+      <c r="A19" s="3">
         <v>6077</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="7">
+      <c r="A20" s="3">
         <v>7020</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="3" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="7">
+      <c r="A21" s="3">
         <v>7021</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="7">
+      <c r="A22" s="3">
         <v>7022</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="7">
+      <c r="A23" s="3">
         <v>7023</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="7">
+      <c r="A24" s="3">
         <v>9000</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="7">
+      <c r="A25" s="3">
         <v>9454</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="7">
+      <c r="A26" s="3">
         <v>10022</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="7">
+      <c r="A27" s="3">
         <v>10023</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="7">
+      <c r="A28" s="3">
         <v>10024</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="7">
+      <c r="A29" s="3">
         <v>10025</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="7">
+      <c r="A30" s="3">
         <v>10026</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="7">
+      <c r="A31" s="3">
         <v>10114</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="7">
+      <c r="A32" s="3">
         <v>13499</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="7">
+      <c r="A33" s="3">
         <v>13500</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="7">
+      <c r="A34" s="3">
         <v>13501</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="7">
+      <c r="A35" s="3">
         <v>13503</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="7">
+      <c r="A36" s="3">
         <v>13590</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="3" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="7">
+      <c r="A37" s="3">
         <v>13591</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="3" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="7">
+      <c r="A38" s="3">
         <v>13592</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="7">
+      <c r="A39" s="3">
         <v>13594</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="3" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7">
+      <c r="A40" s="3">
         <v>13667</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="7">
+      <c r="A41" s="3">
         <v>13799</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="7">
+      <c r="A42" s="3">
         <v>13800</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="3" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="7">
+      <c r="A43" s="3">
         <v>13801</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="7">
+      <c r="A44" s="3">
         <v>13803</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="7">
+      <c r="A45" s="3">
         <v>13821</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="7">
+      <c r="A46" s="3">
         <v>13822</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="7">
+      <c r="A47" s="3">
         <v>13823</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="7">
+      <c r="A48" s="3">
         <v>13825</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="7">
+      <c r="A49" s="3">
         <v>14023</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="7">
+      <c r="A50" s="3">
         <v>14024</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="3" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="7">
+      <c r="A51" s="3">
         <v>14025</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="7">
+      <c r="A52" s="3">
         <v>14027</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="3" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="3">
+        <v>10528</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="3">
+        <v>10529</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="3">
+        <v>10530</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="3">
+        <v>10533</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="3">
+        <v>3701</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="3">
+        <v>3702</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="3">
+        <v>3317</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="3">
+        <v>3974</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="3">
+        <v>4014</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="3">
+        <v>7042</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="3">
+        <v>10512</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="3">
+        <v>10519</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="3">
+        <v>12691</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="3">
+        <v>12692</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="3">
+        <v>12693</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="3">
+        <v>12696</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="3">
+        <v>12697</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="3">
+        <v>10514</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="3">
+        <v>10518</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="3">
+        <v>12863</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="3">
+        <v>12864</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="3">
+        <v>12865</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="3">
+        <v>12866</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="3">
+        <v>12869</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="3">
+        <v>6073</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="3">
+        <v>6074</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="3">
+        <v>6075</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="3">
+        <v>6076</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="3">
+        <v>6607</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="3">
+        <v>6608</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="3">
+        <v>6609</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="3">
+        <v>8728</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="3">
+        <v>9534</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="3">
+        <v>11108</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="3">
+        <v>10516</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="3">
+        <v>10520</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="3">
+        <v>13055</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="3">
+        <v>13056</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="3">
+        <v>13057</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="3">
+        <v>13060</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="3">
+        <v>1547</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="3">
+        <v>1548</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="3">
+        <v>1549</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="3">
+        <v>1550</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="3">
+        <v>1551</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="3">
+        <v>10515</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="3">
+        <v>10521</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="3">
+        <v>13381</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="3">
+        <v>13382</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="3">
+        <v>13383</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="3">
+        <v>13384</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="3">
+        <v>13295</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="3">
+        <v>10513</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="3">
+        <v>10517</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0FE877-D45E-4F3D-96E5-6AF40D6D9A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677AB525-AB36-4046-833A-9484AFAB31BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
     <sheet name="素材名と図鑑番号の対応" sheetId="2" r:id="rId2"/>
+    <sheet name="お知らせ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="232">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -2535,11 +2536,52 @@
     <t>創装の宝玉,ダイヤドラゴンフルーツ,古代の三神面(×5),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ,ニジピィ(×5(※)),火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2～3)</t>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>祝　実装</t>
+    <rPh sb="0" eb="1">
+      <t>シュク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アナウンス(タイトル)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アナウンス(本文)</t>
+    <rPh sb="6" eb="8">
+      <t>ホンブン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>本日より実装です。</t>
+    <rPh sb="0" eb="2">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3192,7 +3234,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3255,6 +3297,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -5135,4 +5183,42 @@
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FCBD9B-5783-443C-87DE-4B13994EA8C3}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="17.08203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="21">
+        <v>46264</v>
+      </c>
+      <c r="B2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677AB525-AB36-4046-833A-9484AFAB31BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146F7C78-A54D-41AE-93C4-E8EA01CD88BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="お知らせ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="321">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -84,16 +85,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ボス・部位破壊</t>
-    <rPh sb="3" eb="5">
-      <t>ブイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハカイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>確率ドロップ</t>
     <rPh sb="0" eb="2">
       <t>カクリツ</t>
@@ -289,13 +280,6 @@
     <t>42億</t>
     <rPh sb="2" eb="3">
       <t>オク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>経験値ストック</t>
-    <rPh sb="0" eb="3">
-      <t>ケイケンチ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -2574,15 +2558,1120 @@
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>再臨の超星</t>
+    <rPh sb="0" eb="1">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>リン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煉燼の百龍</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>浄罪の千龍</t>
+    <rPh sb="0" eb="1">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ザイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>深遠の万龍</t>
+    <rPh sb="0" eb="1">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>星砕の兆龍</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>クダ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>伍窮の億兆龍</t>
+    <rPh sb="0" eb="1">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オクチョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体</t>
+    <rPh sb="0" eb="2">
+      <t>ボウラン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴクアク</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>セイメイタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陽</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陰</t>
+    <rPh sb="0" eb="1">
+      <t>イン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煉燼の百式龍・ビャクレンコウ：50周</t>
+    <rPh sb="4" eb="5">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>浄罪の千手龍・センキョウ：50周</t>
+    <rPh sb="4" eb="5">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>深遠の万寿龍・クーバンシェン：50周</t>
+    <rPh sb="0" eb="1">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マンジュ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>星砕の凶兆龍・ゼンチョウガ：50周</t>
+    <rPh sb="3" eb="5">
+      <t>キョウチョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>緋窮の億兆龍・アグリゲート, 蒼窮の億兆龍・アグリゲート,翠窮の億兆龍・アグリゲート,煌窮の億兆龍・アグリゲート,冥窮の億兆龍・アグリゲート：それぞれ約65周(最速で13周)</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ミドリ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>キラ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>サイソク</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体・ゴクレグス：50周,フリングホルニ：20周</t>
+    <rPh sb="0" eb="2">
+      <t>ボウラン</t>
+    </rPh>
+    <rPh sb="3" eb="8">
+      <t>ゴクアクセイメイタイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/625</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/1000</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【回復タイプ強化】,回復タイプのHP1.5倍</t>
+    <rPh sb="1" eb="3">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/2</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【神タイプ強化】,神タイプのHP1.5倍</t>
+    <rPh sb="1" eb="2">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約1/1428</t>
+    <rPh sb="0" eb="1">
+      <t>ヤク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/4</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【体力タイプ強化】,体力タイプのHP1.5倍</t>
+    <rPh sb="1" eb="3">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約1/1666</t>
+    <rPh sb="0" eb="1">
+      <t>ヤク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【バランスタイプ強化】,バランスタイプのHP1.5倍</t>
+    <rPh sb="8" eb="10">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>6,000万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>20億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1億</t>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煉燼の百式龍・ビャクレンコウの希石(ボス本体)</t>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煉燼の百式龍・ビャクレンコウの希石</t>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レインボーメタルドラゴン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レインボーメタルドラゴン(×1),潜在たまドラ☆スキル遅延耐性(×3)</t>
+    <rPh sb="17" eb="19">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>チエンタイセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キングたまドラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆神キラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カミ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆ドラゴンキラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆悪魔キラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>アクマ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆マシンキラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆バランスキラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆攻撃キラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆体力キラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆回復キラー</t>
+    <rPh sb="0" eb="2">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン,キングたまドラ(×4),潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×6),潜在たまドラ☆HP強化++,潜在たまドラ☆攻撃強化++,潜在たまドラ☆回復強化++(×2),潜在たまドラ☆神キラー,潜在たまドラ☆ドラゴンキラー,潜在たまドラ☆悪魔キラー,潜在たまドラ☆マシンキラー,潜在たまドラ☆バランスキラー,潜在たまドラ☆攻撃キラー,潜在たまドラ☆体力キラー,潜在たまドラ☆回復キラー(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>6,500万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>40億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>浄罪の千手龍・センキョウの希石(ボス本体)</t>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆枠解放(×2),ニジピィ(×2),潜在たまドラ☆スキル遅延耐性(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>浄罪の千手龍・センキョウの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センテ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>7,500万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>深遠の万寿龍・クーバンシェンの希石(ボス本体)</t>
+    <rPh sb="0" eb="2">
+      <t>シンエン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マンジュ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レインボーメタルドラゴン(×1),スーパ―ノエルドラゴン(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆神キラー,潜在たまドラ☆ドラゴンキラー,潜在たまドラ☆悪魔キラー,潜在たまドラ☆マシンキラー,潜在たまドラ☆バランスキラー,潜在たまドラ☆攻撃キラー,潜在たまドラ☆体力キラー,潜在たまドラ☆回復キラー(×5),潜在たまドラ☆スキルブースト++,潜在たまドラ☆アシスト無効回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>深遠の万寿龍・クーバンシェンの希石</t>
+    <rPh sb="0" eb="2">
+      <t>シンエン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>マンジュリュウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>星砕の凶兆龍・ゼンチョウガの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>クダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウチョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>凶玉</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ダマ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サラマンダー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>シーサーペント</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドラゴネット</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>七星龍・チィリン=ドラゴンの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ナナ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>創壊神・ブラフマー=ドラゴンの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>静夜龍・シェヘラザード=ドラゴンの希石</t>
+    <rPh sb="0" eb="1">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>惑乱神・エリス=ドラゴンの希石</t>
+    <rPh sb="0" eb="1">
+      <t>マド</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>狛犬龍・センリ=ドラゴンの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ハク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>イヌ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>星砕の凶兆龍・ゼンチョウガの希石(ボス本体),凶玉(×2(ボス部位))</t>
+    <rPh sb="19" eb="21">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サゲピィ,とじたまドラ,モドリット(×1),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×5),サラマンダー,シーサーペント,ドラゴネット(×1),七星龍・チィリン=ドラゴンの希石,静夜龍・シェヘラザード=ドラゴンの希石,創壊神・ブラフマー=ドラゴンの希石,惑乱神・エリス=ドラゴンの希石,狛犬龍・センリ=ドラゴンの希石(×1),潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆ダメージ吸収貫通,潜在たまドラ☆ルーレット回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆スキルブースト++,潜在たまドラ☆アシスト無効回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煌窮の億兆龍・アグリゲートの希石</t>
+    <rPh sb="0" eb="1">
+      <t>キラ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>冥窮の億兆龍・アグリゲートの希石</t>
+    <rPh sb="0" eb="1">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>緋窮の億兆龍・アグリゲートの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼窮の億兆龍・アグリゲートの希石</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>翠窮の億兆龍・アグリゲートの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ミドリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>7,700万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>42億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>43億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>経験値ストック</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパ―ノエルドラゴン(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパ―ノエルドラゴン(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゴールドたまドラ(×1～2),キングゴールドドラゴンズ(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×7～10(※2))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煌窮の億兆龍・アグリゲートの希石,冥窮の億兆龍・アグリゲートの希石,緋窮の億兆龍・アグリゲートの希石, 蒼窮の億兆龍・アグリゲートの希石,翠窮の億兆龍・アグリゲートの希石(×4(※1))</t>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※1ランダム1色が4個ドロップする。その内訳は、ボス本体×1 + ボス部位×3。,※2確率ドロップのゴールドたまドラ、キングゴールドドラゴンズのドロップ数で増減する？</t>
+    <rPh sb="7" eb="8">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ウチワケ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ゾウゲン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体・ゴクレグスの希石</t>
+    <rPh sb="0" eb="2">
+      <t>ボウラン</t>
+    </rPh>
+    <rPh sb="3" eb="8">
+      <t>ゴクアクセイメイタイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ボス・乱入・部位破壊</t>
+    <rPh sb="3" eb="5">
+      <t>ランニュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハカイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>バルドル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>フリングホルニの希石</t>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体・ゴクレグスの希石(ボス本体),バルドル(乱入本体),フリングホルニの希石(乱入部位)</t>
+    <rPh sb="20" eb="22">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ランニュウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="46" eb="50">
+      <t>ランニュウブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ニジピィ(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>創装の宝玉,ダイヤドラゴンフルーツ,古代の三神面(×2(※2)),サゲピィ,とじたまドラ,モドリット(×1),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×8(※1)(※2))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4(※2))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※1極キングルビードラゴン、極キングサファイアドラゴン、極エメラルドドラゴンは確定で各2体ドロップする。極キングゴールドドラゴン、極キングメタルドラゴンはいずれか一方がドロップし、それが2回続く。(何属性が落ちるかは1Fと6Fで出たモンスターの属性を見ればわかります。)(※1の説明を報酬リストに組み込むとややこしくなるため簡潔な表記にしています。),※2表記した数は最大値です。乱入が3Fのとき属性軽減たまドラが1体、6Fのとき極キング○○○ドラゴンが4体、9Fで創装の宝玉らのランダムドロップが1体減少する。(属性軽減たまドラは不確定ドロップであるため、ドロップ数が0になることもある。)</t>
+    <rPh sb="2" eb="3">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>イッポウ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="99" eb="102">
+      <t>ナニゾクセイ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="125" eb="126">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="148" eb="149">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>カンケツ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="178" eb="180">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="182" eb="183">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="184" eb="187">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="190" eb="192">
+      <t>ランニュウ</t>
+    </rPh>
+    <rPh sb="198" eb="200">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>ケイゲン</t>
+    </rPh>
+    <rPh sb="208" eb="209">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="215" eb="216">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="228" eb="229">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.5億</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>50億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2748,6 +3837,14 @@
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2937,7 +4034,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -3102,6 +4199,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3234,7 +4340,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3265,9 +4371,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3298,11 +4401,42 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3680,22 +4814,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="18.58203125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="10.58203125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" style="18" customWidth="1"/>
-    <col min="6" max="6" width="108.75" style="18" customWidth="1"/>
-    <col min="7" max="8" width="30.58203125" style="19" customWidth="1"/>
-    <col min="9" max="9" width="75.58203125" style="18" customWidth="1"/>
-    <col min="10" max="14" width="25.58203125" style="18" customWidth="1"/>
-    <col min="15" max="15" width="163.75" style="17" customWidth="1"/>
-    <col min="16" max="16" width="71.1640625" style="17" customWidth="1"/>
-    <col min="17" max="17" width="69.08203125" style="17" customWidth="1"/>
-    <col min="18" max="18" width="255.5" style="17" customWidth="1"/>
-    <col min="19" max="19" width="102.5" style="17" customWidth="1"/>
-    <col min="20" max="20" width="104.1640625" style="17" customWidth="1"/>
+    <col min="3" max="4" width="10.58203125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="10.58203125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="156.4140625" style="17" customWidth="1"/>
+    <col min="7" max="8" width="30.58203125" style="18" customWidth="1"/>
+    <col min="9" max="9" width="75.58203125" style="17" customWidth="1"/>
+    <col min="10" max="14" width="25.58203125" style="17" customWidth="1"/>
+    <col min="15" max="15" width="163.75" style="16" customWidth="1"/>
+    <col min="16" max="16" width="71.1640625" style="16" customWidth="1"/>
+    <col min="17" max="17" width="69.08203125" style="16" customWidth="1"/>
+    <col min="18" max="18" width="255.5" style="16" customWidth="1"/>
+    <col min="19" max="19" width="151.1640625" style="16" customWidth="1"/>
+    <col min="20" max="20" width="104.1640625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3709,55 +4843,55 @@
         <v>8</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="J1" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M1" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3767,50 +4901,50 @@
       <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <v>99</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>12</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="12">
+      <c r="H2" s="10"/>
+      <c r="I2" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="11">
         <v>2970</v>
       </c>
-      <c r="M2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="13" t="s">
+      <c r="M2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="11"/>
+      <c r="O2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
     </row>
     <row r="3" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6" t="s">
@@ -3819,104 +4953,104 @@
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>99</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>15</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="12">
+      <c r="E3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="11">
         <v>2970</v>
       </c>
-      <c r="M3" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="13" t="s">
+      <c r="M3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="Q3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="R3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
     </row>
     <row r="4" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="9">
+        <v>99</v>
+      </c>
+      <c r="D4" s="9">
+        <v>12</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="O4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="10">
-        <v>99</v>
-      </c>
-      <c r="D4" s="10">
-        <v>12</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="12">
-        <v>2970</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="Q4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
     </row>
     <row r="5" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6" t="s">
@@ -3925,53 +5059,53 @@
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>99</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>15</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G5" s="11" t="s">
+      <c r="E5" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="12">
+      <c r="I5" s="9"/>
+      <c r="J5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="11">
         <v>6666</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="13" t="s">
+      <c r="M5" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="11"/>
+      <c r="O5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="S5" s="14"/>
-      <c r="T5" s="13" t="s">
-        <v>42</v>
+      <c r="R5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" s="13"/>
+      <c r="T5" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3981,329 +5115,646 @@
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>99</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>15</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="12">
+      <c r="E6" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="11">
         <v>2970</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="12">
+      <c r="M6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="N6" s="11">
+        <v>30</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="R6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R6" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" s="14"/>
-      <c r="T6" s="13" t="s">
-        <v>43</v>
+      <c r="S6" s="13"/>
+      <c r="T6" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="10">
+        <v>121</v>
+      </c>
+      <c r="C7" s="9">
         <v>99</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>12</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="K7" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <v>2970</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="13" t="s">
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q7" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="P7" s="13" t="s">
+      <c r="R7" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="Q7" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="R7" s="13" t="s">
+      <c r="S7" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="S7" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="T7" s="14"/>
+      <c r="T7" s="13"/>
     </row>
     <row r="8" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>99</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>13</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="L8" s="12">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="11">
         <v>2970</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="13" t="s">
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="R8" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="P8" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q8" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="T8" s="14"/>
+      <c r="S8" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="T8" s="13"/>
     </row>
     <row r="9" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="10">
+        <v>123</v>
+      </c>
+      <c r="C9" s="9">
         <v>99</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>13</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="L9" s="12">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9" s="11">
         <v>7777</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="13" t="s">
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q9" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="R9" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="Q9" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
     </row>
     <row r="10" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="9">
+        <v>99</v>
+      </c>
+      <c r="D10" s="9">
+        <v>14</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="10">
-        <v>99</v>
-      </c>
-      <c r="D10" s="10">
-        <v>14</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="L10" s="12">
+      <c r="H10" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="L10" s="11">
         <v>5000</v>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="13" t="s">
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="R10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="P10" s="13" t="s">
+      <c r="S10" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="Q10" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="S10" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="T10" s="14"/>
+      <c r="T10" s="13"/>
     </row>
     <row r="11" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="10">
+        <v>125</v>
+      </c>
+      <c r="C11" s="9">
         <v>99</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>15</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" s="10" t="s">
+      <c r="E11" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="L11" s="12">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="L11" s="11">
         <v>9999</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="13" t="s">
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q11" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="R11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="T11" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="Q11" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="S11" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="T11" s="13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    </row>
+    <row r="12" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="9">
+        <v>99</v>
+      </c>
+      <c r="D12" s="9">
+        <v>9</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="L12" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="N12" s="9"/>
+      <c r="O12" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+    </row>
+    <row r="13" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="9">
+        <v>99</v>
+      </c>
+      <c r="D13" s="9">
+        <v>10</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L13" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+    </row>
+    <row r="14" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="9">
+        <v>99</v>
+      </c>
+      <c r="D14" s="9">
+        <v>11</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L14" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="N14" s="9"/>
+      <c r="O14" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+    </row>
+    <row r="15" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="9">
+        <v>99</v>
+      </c>
+      <c r="D15" s="9">
+        <v>12</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="L15" s="11">
+        <v>6600</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="N15" s="9"/>
+      <c r="O15" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+    </row>
+    <row r="16" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C16" s="9">
+        <v>99</v>
+      </c>
+      <c r="D16" s="9">
+        <v>12</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="L16" s="11">
+        <v>5555</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="N16" s="9"/>
+      <c r="O16" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="S16" s="26"/>
+      <c r="T16" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="25" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="9">
+        <v>99</v>
+      </c>
+      <c r="D17" s="23">
+        <v>13</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="L17" s="30">
+        <v>7777</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="N17" s="23"/>
+      <c r="O17" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="P17" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="S17" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="T17" s="29" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="19" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="20" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="21" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="22" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="23" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="24" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4313,7 +5764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -4322,10 +5773,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4333,7 +5784,7 @@
         <v>1077</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4341,7 +5792,7 @@
         <v>1081</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4349,7 +5800,7 @@
         <v>1083</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4357,7 +5808,7 @@
         <v>1709</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4365,7 +5816,7 @@
         <v>2250</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4373,7 +5824,7 @@
         <v>2425</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4381,7 +5832,7 @@
         <v>3795</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4389,7 +5840,7 @@
         <v>3891</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4397,7 +5848,7 @@
         <v>3911</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4405,7 +5856,7 @@
         <v>3971</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4413,7 +5864,7 @@
         <v>3973</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4421,7 +5872,7 @@
         <v>4369</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4429,7 +5880,7 @@
         <v>4370</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4437,7 +5888,7 @@
         <v>4371</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4445,7 +5896,7 @@
         <v>4372</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4453,7 +5904,7 @@
         <v>4373</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4461,7 +5912,7 @@
         <v>5739</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4469,7 +5920,7 @@
         <v>6077</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4477,7 +5928,7 @@
         <v>7020</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4485,7 +5936,7 @@
         <v>7021</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4493,7 +5944,7 @@
         <v>7022</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4501,7 +5952,7 @@
         <v>7023</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4509,7 +5960,7 @@
         <v>9000</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4517,7 +5968,7 @@
         <v>9454</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4525,7 +5976,7 @@
         <v>10022</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4533,7 +5984,7 @@
         <v>10023</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4541,7 +5992,7 @@
         <v>10024</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4549,7 +6000,7 @@
         <v>10025</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4557,7 +6008,7 @@
         <v>10026</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4565,7 +6016,7 @@
         <v>10114</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4573,7 +6024,7 @@
         <v>13499</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4581,7 +6032,7 @@
         <v>13500</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4589,7 +6040,7 @@
         <v>13501</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4597,7 +6048,7 @@
         <v>13503</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4605,7 +6056,7 @@
         <v>13590</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4613,7 +6064,7 @@
         <v>13591</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4621,7 +6072,7 @@
         <v>13592</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4629,7 +6080,7 @@
         <v>13594</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4637,7 +6088,7 @@
         <v>13667</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4645,7 +6096,7 @@
         <v>13799</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4653,7 +6104,7 @@
         <v>13800</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4661,7 +6112,7 @@
         <v>13801</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4669,7 +6120,7 @@
         <v>13803</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4677,7 +6128,7 @@
         <v>13821</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4685,7 +6136,7 @@
         <v>13822</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4693,7 +6144,7 @@
         <v>13823</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4701,7 +6152,7 @@
         <v>13825</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4709,7 +6160,7 @@
         <v>14023</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4717,7 +6168,7 @@
         <v>14024</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4725,7 +6176,7 @@
         <v>14025</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4733,7 +6184,7 @@
         <v>14027</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4741,7 +6192,7 @@
         <v>10528</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4749,7 +6200,7 @@
         <v>10529</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4757,7 +6208,7 @@
         <v>10530</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4765,7 +6216,7 @@
         <v>10533</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4773,7 +6224,7 @@
         <v>3700</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4781,7 +6232,7 @@
         <v>3701</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4789,7 +6240,7 @@
         <v>3702</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4797,7 +6248,7 @@
         <v>3317</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4805,7 +6256,7 @@
         <v>3974</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4813,7 +6264,7 @@
         <v>4014</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4821,7 +6272,7 @@
         <v>7042</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4829,7 +6280,7 @@
         <v>10512</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4837,7 +6288,7 @@
         <v>10519</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4845,7 +6296,7 @@
         <v>12691</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4853,7 +6304,7 @@
         <v>12692</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4861,7 +6312,7 @@
         <v>12693</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4869,7 +6320,7 @@
         <v>12696</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4877,7 +6328,7 @@
         <v>12697</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4885,7 +6336,7 @@
         <v>10514</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4893,7 +6344,7 @@
         <v>10518</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4901,7 +6352,7 @@
         <v>12863</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4909,7 +6360,7 @@
         <v>12864</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4917,7 +6368,7 @@
         <v>12865</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4925,7 +6376,7 @@
         <v>12866</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4933,7 +6384,7 @@
         <v>12869</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4941,7 +6392,7 @@
         <v>6073</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4949,7 +6400,7 @@
         <v>6074</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4957,7 +6408,7 @@
         <v>6075</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4965,7 +6416,7 @@
         <v>6076</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4973,7 +6424,7 @@
         <v>6607</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4981,7 +6432,7 @@
         <v>6608</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4989,7 +6440,7 @@
         <v>6609</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4997,7 +6448,7 @@
         <v>8728</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5005,7 +6456,7 @@
         <v>9534</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5013,7 +6464,7 @@
         <v>11108</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5021,7 +6472,7 @@
         <v>10516</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5029,7 +6480,7 @@
         <v>10520</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5037,7 +6488,7 @@
         <v>13055</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5045,7 +6496,7 @@
         <v>13056</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5053,7 +6504,7 @@
         <v>13057</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5061,7 +6512,7 @@
         <v>13060</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5069,7 +6520,7 @@
         <v>1547</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5077,7 +6528,7 @@
         <v>1548</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5085,7 +6536,7 @@
         <v>1549</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5093,7 +6544,7 @@
         <v>1550</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5101,7 +6552,7 @@
         <v>1551</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5109,7 +6560,7 @@
         <v>10515</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5117,7 +6568,7 @@
         <v>10521</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5125,7 +6576,7 @@
         <v>13381</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5133,7 +6584,7 @@
         <v>13382</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5141,7 +6592,7 @@
         <v>13383</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5149,7 +6600,7 @@
         <v>13384</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5157,7 +6608,7 @@
         <v>13295</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5165,15 +6616,263 @@
         <v>10513</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="3">
+      <c r="A107" s="28">
         <v>10517</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>221</v>
+      <c r="B107" s="28" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="3">
+        <v>11119</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="3">
+        <v>1341</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="3">
+        <v>3827</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="3">
+        <v>3318</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="3">
+        <v>3319</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="3">
+        <v>3320</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="3">
+        <v>3321</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="3">
+        <v>3322</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="3">
+        <v>3323</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="3">
+        <v>3324</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="3">
+        <v>3325</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="3">
+        <v>11196</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="3">
+        <v>11207</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="3">
+        <v>11552</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="3">
+        <v>11588</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="3">
+        <v>112</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="3">
+        <v>114</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" s="3">
+        <v>116</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="3">
+        <v>6178</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" s="3">
+        <v>6878</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="3">
+        <v>6522</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="3">
+        <v>7493</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="3">
+        <v>8298</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="3">
+        <v>11556</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" s="3">
+        <v>11559</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" s="3">
+        <v>11562</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" s="3">
+        <v>11565</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" s="3">
+        <v>11568</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" s="3">
+        <v>12257</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" s="3">
+        <v>12258</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" s="3">
+        <v>12261</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -5190,31 +6889,31 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.08203125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.08203125" style="19" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" t="s">
         <v>227</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="20">
+        <v>46264</v>
+      </c>
+      <c r="B2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" t="s">
         <v>229</v>
-      </c>
-      <c r="C1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="21">
-        <v>46264</v>
-      </c>
-      <c r="B2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146F7C78-A54D-41AE-93C4-E8EA01CD88BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146F7C78-A54D-41AE-93C4-E8EA01CD88BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038D7EC5-FD5D-4CA1-BB02-3BF593F05526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="326">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -3660,6 +3660,86 @@
     <t>50億</t>
     <rPh sb="2" eb="3">
       <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火の希石【巨大】</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水の希石【巨大】</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木の希石【巨大】</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>光の希石【巨大】</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>闇の希石【巨大】</t>
+    <rPh sb="0" eb="1">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -4340,7 +4420,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4437,6 +4517,9 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -5764,7 +5847,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -5781,1103 +5864,1143 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3">
-        <v>1077</v>
+        <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3">
-        <v>1081</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3">
-        <v>1083</v>
+        <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3">
-        <v>1709</v>
+        <v>1077</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
-        <v>2250</v>
+        <v>1081</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3">
-        <v>2425</v>
+        <v>1083</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
-        <v>3795</v>
+        <v>1341</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
-        <v>3891</v>
+        <v>1547</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
-        <v>3911</v>
+        <v>1548</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
-        <v>3971</v>
+        <v>1549</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>59</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
-        <v>3973</v>
+        <v>1550</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
-        <v>4369</v>
+        <v>1551</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
-        <v>4370</v>
+        <v>1709</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
-        <v>4371</v>
+        <v>2250</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
-        <v>4372</v>
+        <v>2425</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
-        <v>4373</v>
+        <v>3317</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
-        <v>5739</v>
+        <v>3318</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>57</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
-        <v>6077</v>
+        <v>3319</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
-        <v>7020</v>
+        <v>3320</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>71</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
-        <v>7021</v>
+        <v>3321</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>48</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
-        <v>7022</v>
+        <v>3322</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>49</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
-        <v>7023</v>
+        <v>3323</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>50</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
-        <v>9000</v>
+        <v>3324</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
-        <v>9454</v>
+        <v>3325</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
-        <v>10022</v>
+        <v>3700</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
-        <v>10023</v>
+        <v>3701</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
-        <v>10024</v>
+        <v>3702</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
-        <v>10025</v>
+        <v>3795</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
-        <v>10026</v>
+        <v>3827</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
-        <v>10114</v>
+        <v>3891</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
-        <v>13499</v>
+        <v>3911</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
-        <v>13500</v>
+        <v>3971</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
-        <v>13501</v>
+        <v>3973</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
-        <v>13503</v>
+        <v>3974</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3">
-        <v>13590</v>
+        <v>4014</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3">
-        <v>13591</v>
+        <v>4369</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
-        <v>13592</v>
+        <v>4370</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
-        <v>13594</v>
+        <v>4371</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3">
-        <v>13667</v>
+        <v>4372</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3">
-        <v>13799</v>
+        <v>4373</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3">
-        <v>13800</v>
+        <v>5739</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3">
-        <v>13801</v>
+        <v>6073</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3">
-        <v>13803</v>
+        <v>6074</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3">
-        <v>13821</v>
+        <v>6075</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3">
-        <v>13822</v>
+        <v>6076</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3">
-        <v>13823</v>
+        <v>6077</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3">
-        <v>13825</v>
+        <v>6178</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>82</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3">
-        <v>14023</v>
+        <v>6522</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>95</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3">
-        <v>14024</v>
+        <v>6607</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>96</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3">
-        <v>14025</v>
+        <v>6608</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3">
-        <v>14027</v>
+        <v>6609</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>98</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3">
-        <v>10528</v>
+        <v>6878</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>152</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3">
-        <v>10529</v>
+        <v>7020</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3">
-        <v>10530</v>
+        <v>7021</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3">
-        <v>10533</v>
+        <v>7022</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>155</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3">
-        <v>3700</v>
+        <v>7023</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3">
-        <v>3701</v>
+        <v>7042</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3">
-        <v>3702</v>
+        <v>7493</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3">
-        <v>3317</v>
+        <v>8298</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>159</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3">
-        <v>3974</v>
+        <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>160</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3">
-        <v>4014</v>
+        <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>161</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3">
-        <v>7042</v>
+        <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>162</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3">
-        <v>10512</v>
+        <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>163</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3">
-        <v>10519</v>
+        <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>164</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3">
-        <v>12691</v>
+        <v>8728</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3">
-        <v>12692</v>
+        <v>9000</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3">
-        <v>12693</v>
+        <v>9454</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>167</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3">
-        <v>12696</v>
+        <v>9534</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3">
-        <v>12697</v>
+        <v>10022</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3">
-        <v>10514</v>
+        <v>10023</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3">
-        <v>10518</v>
+        <v>10024</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>174</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3">
-        <v>12863</v>
+        <v>10025</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3">
-        <v>12864</v>
+        <v>10026</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>177</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3">
-        <v>12865</v>
+        <v>10114</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3">
-        <v>12866</v>
+        <v>10512</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3">
-        <v>12869</v>
+        <v>10513</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3">
-        <v>6073</v>
+        <v>10514</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3">
-        <v>6074</v>
+        <v>10515</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3">
-        <v>6075</v>
+        <v>10516</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="3">
-        <v>6076</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>184</v>
+      <c r="A81" s="31">
+        <v>10517</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3">
-        <v>6607</v>
+        <v>10518</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3">
-        <v>6608</v>
+        <v>10519</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3">
-        <v>6609</v>
+        <v>10520</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3">
-        <v>8728</v>
+        <v>10521</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3">
-        <v>9534</v>
+        <v>10528</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3">
-        <v>11108</v>
+        <v>10529</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3">
-        <v>10516</v>
+        <v>10530</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3">
-        <v>10520</v>
+        <v>10533</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3">
-        <v>13055</v>
+        <v>11108</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3">
-        <v>13056</v>
+        <v>11119</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3">
-        <v>13057</v>
+        <v>11196</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>199</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3">
-        <v>13060</v>
+        <v>11207</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>200</v>
+        <v>282</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3">
-        <v>1547</v>
+        <v>11552</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>201</v>
+        <v>283</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3">
-        <v>1548</v>
+        <v>11556</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>202</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3">
-        <v>1549</v>
+        <v>11559</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>203</v>
+        <v>296</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3">
-        <v>1550</v>
+        <v>11562</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>204</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3">
-        <v>1551</v>
+        <v>11565</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>205</v>
+        <v>298</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3">
-        <v>10515</v>
+        <v>11568</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>206</v>
+        <v>299</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3">
-        <v>10521</v>
+        <v>11588</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>207</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3">
-        <v>13381</v>
+        <v>12257</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>213</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3">
-        <v>13382</v>
+        <v>12258</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>214</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3">
-        <v>13383</v>
+        <v>12261</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>215</v>
+        <v>313</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3">
-        <v>13384</v>
+        <v>12691</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3">
-        <v>13295</v>
+        <v>12692</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3">
-        <v>10513</v>
+        <v>12693</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="28">
-        <v>10517</v>
+        <v>12696</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3">
-        <v>11119</v>
+        <v>12697</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>259</v>
+        <v>169</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3">
-        <v>1341</v>
+        <v>12863</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>260</v>
+        <v>176</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3">
-        <v>3827</v>
+        <v>12864</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>262</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3">
-        <v>3318</v>
+        <v>12865</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>263</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3">
-        <v>3319</v>
+        <v>12866</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>264</v>
+        <v>179</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="3">
-        <v>3320</v>
+        <v>12869</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>265</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="3">
-        <v>3321</v>
+        <v>13055</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>266</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="3">
-        <v>3322</v>
+        <v>13056</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="3">
-        <v>3323</v>
+        <v>13057</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>268</v>
+        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="3">
-        <v>3324</v>
+        <v>13060</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3">
-        <v>3325</v>
+        <v>13295</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3">
-        <v>11196</v>
+        <v>13381</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>277</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3">
-        <v>11207</v>
+        <v>13382</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>282</v>
+        <v>214</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3">
-        <v>11552</v>
+        <v>13383</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>283</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3">
-        <v>11588</v>
+        <v>13384</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>284</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3">
-        <v>112</v>
+        <v>13499</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>285</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3">
-        <v>114</v>
+        <v>13500</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>286</v>
+        <v>88</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="3">
-        <v>116</v>
+        <v>13501</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>287</v>
+        <v>89</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3">
-        <v>6178</v>
+        <v>13503</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>288</v>
+        <v>90</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3">
-        <v>6878</v>
+        <v>13590</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>289</v>
+        <v>83</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3">
-        <v>6522</v>
+        <v>13591</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>290</v>
+        <v>84</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="3">
-        <v>7493</v>
+        <v>13592</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>291</v>
+        <v>85</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="3">
-        <v>8298</v>
+        <v>13594</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>292</v>
+        <v>86</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="3">
-        <v>11556</v>
+        <v>13667</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3">
-        <v>11559</v>
+        <v>13799</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>296</v>
+        <v>91</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3">
-        <v>11562</v>
+        <v>13800</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>297</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="3">
-        <v>11565</v>
+        <v>13801</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>298</v>
+        <v>93</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="3">
-        <v>11568</v>
+        <v>13803</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>299</v>
+        <v>94</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="3">
-        <v>12257</v>
+        <v>13821</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>310</v>
+        <v>79</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="3">
-        <v>12258</v>
+        <v>13822</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>312</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="3">
-        <v>12261</v>
+        <v>13823</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>313</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" s="3">
+        <v>13825</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A140" s="3">
+        <v>14023</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" s="3">
+        <v>14024</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" s="3">
+        <v>14025</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" s="3">
+        <v>14027</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B52">
-    <sortCondition ref="A2:A52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B143">
+    <sortCondition ref="A2:A143"/>
   </sortState>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038D7EC5-FD5D-4CA1-BB02-3BF593F05526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900693F0-BDE7-4161-BB1A-C0A1FB0D9020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="お知らせ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1859,70 +1858,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×2)</t>
-    <rPh sb="0" eb="1">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キョダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>キョダイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>キョダイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キョダイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ヤミ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>キョダイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>風魔斧・アクスロン</t>
     <rPh sb="0" eb="2">
       <t>フウマ</t>
@@ -3052,10 +2987,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×1)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>浄罪の千手龍・センキョウの希石</t>
     <rPh sb="0" eb="1">
       <t>ジョウ</t>
@@ -3739,6 +3670,74 @@
       <t>セキ</t>
     </rPh>
     <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×1)</t>
+    <rPh sb="9" eb="10">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火の希石【巨大】,水の希石,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×2)</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
       <t>キョダイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
@@ -4420,7 +4419,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4487,38 +4486,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4953,13 +4924,13 @@
         <v>33</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>38</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>11</v>
@@ -5343,10 +5314,10 @@
         <v>171</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>172</v>
+        <v>325</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>151</v>
@@ -5389,16 +5360,16 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="P9" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="Q9" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="Q9" s="12" t="s">
+      <c r="R9" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="S9" s="13"/>
       <c r="T9" s="13"/>
@@ -5441,19 +5412,19 @@
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="P10" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="Q10" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="R10" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="Q10" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="R10" s="12" t="s">
+      <c r="S10" s="12" t="s">
         <v>210</v>
-      </c>
-      <c r="S10" s="12" t="s">
-        <v>211</v>
       </c>
       <c r="T10" s="13"/>
     </row>
@@ -5495,30 +5466,30 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="P11" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="Q11" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="Q11" s="12" t="s">
-        <v>222</v>
-      </c>
       <c r="R11" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>150</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>230</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>231</v>
       </c>
       <c r="C12" s="9">
         <v>99</v>
@@ -5527,48 +5498,48 @@
         <v>9</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>255</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>256</v>
       </c>
       <c r="L12" s="11">
         <v>2970</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q12" s="26"/>
+        <v>260</v>
+      </c>
+      <c r="Q12" s="13"/>
       <c r="R12" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
+        <v>270</v>
+      </c>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
     </row>
     <row r="13" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C13" s="9">
         <v>99</v>
@@ -5577,21 +5548,21 @@
         <v>10</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="K13" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="L13" s="11">
         <v>2970</v>
@@ -5599,24 +5570,24 @@
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="P13" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="P13" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q13" s="26"/>
+      <c r="Q13" s="13"/>
       <c r="R13" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="S13" s="26"/>
-      <c r="T13" s="26"/>
+        <v>324</v>
+      </c>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
     </row>
     <row r="14" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C14" s="9">
         <v>99</v>
@@ -5625,50 +5596,50 @@
         <v>11</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L14" s="11">
         <v>2970</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="P14" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
     </row>
     <row r="15" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C15" s="9">
         <v>99</v>
@@ -5677,52 +5648,52 @@
         <v>12</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H15" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="J15" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L15" s="11">
         <v>6600</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q15" s="26"/>
+        <v>302</v>
+      </c>
+      <c r="Q15" s="13"/>
       <c r="R15" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
+        <v>292</v>
+      </c>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
     </row>
     <row r="16" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C16" s="9">
         <v>99</v>
@@ -5732,103 +5703,103 @@
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="I16" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>252</v>
-      </c>
       <c r="J16" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L16" s="11">
         <v>5555</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P16" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="R16" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="Q16" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="R16" s="12" t="s">
+      <c r="S16" s="13"/>
+      <c r="T16" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="S16" s="26"/>
-      <c r="T16" s="12" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" s="25" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>236</v>
+        <v>229</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="C17" s="9">
         <v>99</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="9">
         <v>13</v>
       </c>
-      <c r="E17" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="G17" s="24" t="s">
+      <c r="E17" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="I17" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="H17" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="J17" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="K17" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="L17" s="30">
+      <c r="J17" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="L17" s="11">
         <v>7777</v>
       </c>
-      <c r="M17" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="N17" s="23"/>
-      <c r="O17" s="29" t="s">
+      <c r="M17" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="N17" s="9"/>
+      <c r="O17" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="P17" s="29" t="s">
+      <c r="S17" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="29" t="s">
+      <c r="T17" s="12" t="s">
         <v>316</v>
-      </c>
-      <c r="S17" s="29" t="s">
-        <v>317</v>
-      </c>
-      <c r="T17" s="29" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -5867,7 +5838,7 @@
         <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5875,7 +5846,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5883,7 +5854,7 @@
         <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5915,7 +5886,7 @@
         <v>1341</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5923,7 +5894,7 @@
         <v>1547</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5931,7 +5902,7 @@
         <v>1548</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5939,7 +5910,7 @@
         <v>1549</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5947,7 +5918,7 @@
         <v>1550</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5955,7 +5926,7 @@
         <v>1551</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5995,7 +5966,7 @@
         <v>3318</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6003,7 +5974,7 @@
         <v>3319</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6011,7 +5982,7 @@
         <v>3320</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6019,7 +5990,7 @@
         <v>3321</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6027,7 +5998,7 @@
         <v>3322</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6035,7 +6006,7 @@
         <v>3323</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6043,7 +6014,7 @@
         <v>3324</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6051,7 +6022,7 @@
         <v>3325</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6091,7 +6062,7 @@
         <v>3827</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6195,7 +6166,7 @@
         <v>6073</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6203,7 +6174,7 @@
         <v>6074</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6211,7 +6182,7 @@
         <v>6075</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6219,7 +6190,7 @@
         <v>6076</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6235,7 +6206,7 @@
         <v>6178</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6243,7 +6214,7 @@
         <v>6522</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6251,7 +6222,7 @@
         <v>6607</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6259,7 +6230,7 @@
         <v>6608</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6267,7 +6238,7 @@
         <v>6609</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6275,7 +6246,7 @@
         <v>6878</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6323,7 +6294,7 @@
         <v>7493</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6331,7 +6302,7 @@
         <v>8298</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6339,7 +6310,7 @@
         <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6347,7 +6318,7 @@
         <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6355,7 +6326,7 @@
         <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6363,7 +6334,7 @@
         <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6371,7 +6342,7 @@
         <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6379,7 +6350,7 @@
         <v>8728</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6403,7 +6374,7 @@
         <v>9534</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6467,7 +6438,7 @@
         <v>10513</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6475,7 +6446,7 @@
         <v>10514</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6483,7 +6454,7 @@
         <v>10515</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6491,15 +6462,15 @@
         <v>10516</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="31">
+      <c r="A81" s="3">
         <v>10517</v>
       </c>
-      <c r="B81" s="31" t="s">
-        <v>219</v>
+      <c r="B81" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6507,7 +6478,7 @@
         <v>10518</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6523,7 +6494,7 @@
         <v>10520</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6531,7 +6502,7 @@
         <v>10521</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6571,7 +6542,7 @@
         <v>11108</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6579,7 +6550,7 @@
         <v>11119</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6587,7 +6558,7 @@
         <v>11196</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6595,7 +6566,7 @@
         <v>11207</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6603,7 +6574,7 @@
         <v>11552</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6611,7 +6582,7 @@
         <v>11556</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6619,7 +6590,7 @@
         <v>11559</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6627,7 +6598,7 @@
         <v>11562</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6635,7 +6606,7 @@
         <v>11565</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6643,7 +6614,7 @@
         <v>11568</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6651,7 +6622,7 @@
         <v>11588</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6659,7 +6630,7 @@
         <v>12257</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6667,7 +6638,7 @@
         <v>12258</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6675,7 +6646,7 @@
         <v>12261</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6703,10 +6674,10 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="28">
+      <c r="A107" s="22">
         <v>12696</v>
       </c>
-      <c r="B107" s="28" t="s">
+      <c r="B107" s="22" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6723,7 +6694,7 @@
         <v>12863</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6731,7 +6702,7 @@
         <v>12864</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6739,7 +6710,7 @@
         <v>12865</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6747,7 +6718,7 @@
         <v>12866</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6755,7 +6726,7 @@
         <v>12869</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6763,7 +6734,7 @@
         <v>13055</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6771,7 +6742,7 @@
         <v>13056</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6779,7 +6750,7 @@
         <v>13057</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6787,7 +6758,7 @@
         <v>13060</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6795,7 +6766,7 @@
         <v>13295</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6803,7 +6774,7 @@
         <v>13381</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6811,7 +6782,7 @@
         <v>13382</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6819,7 +6790,7 @@
         <v>13383</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6827,7 +6798,7 @@
         <v>13384</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -7019,13 +6990,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" t="s">
         <v>227</v>
-      </c>
-      <c r="C1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -7033,10 +7004,10 @@
         <v>46264</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900693F0-BDE7-4161-BB1A-C0A1FB0D9020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBE1073-2871-4AA1-8442-359E0168F431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -4113,7 +4113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -4275,15 +4275,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4489,7 +4480,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBE1073-2871-4AA1-8442-359E0168F431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1567DDE9-D7D0-49A5-92DF-CC01CEFCA5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -1858,6 +1858,70 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
+    <t>火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×2)</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
     <t>風魔斧・アクスロン</t>
     <rPh sb="0" eb="2">
       <t>フウマ</t>
@@ -3678,67 +3742,6 @@
     <t>火の希石【巨大】,水の希石【巨大】,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×1)</t>
     <rPh sb="9" eb="10">
       <t>ミズ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>火の希石【巨大】,水の希石,木の希石【巨大】,光の希石【巨大】,闇の希石【巨大】(×2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×2)</t>
-    <rPh sb="0" eb="1">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キョダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>キョダイ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>キョダイ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ヤミ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>キョダイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -4915,13 +4918,13 @@
         <v>33</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>38</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>11</v>
@@ -5305,10 +5308,10 @@
         <v>171</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>325</v>
+        <v>172</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>151</v>
@@ -5351,16 +5354,16 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R9" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S9" s="13"/>
       <c r="T9" s="13"/>
@@ -5403,19 +5406,19 @@
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q10" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="S10" s="12" t="s">
         <v>211</v>
-      </c>
-      <c r="R10" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="S10" s="12" t="s">
-        <v>210</v>
       </c>
       <c r="T10" s="13"/>
     </row>
@@ -5457,30 +5460,30 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R11" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>150</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C12" s="9">
         <v>99</v>
@@ -5489,48 +5492,48 @@
         <v>9</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L12" s="11">
         <v>2970</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S12" s="13"/>
       <c r="T12" s="13"/>
     </row>
     <row r="13" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C13" s="9">
         <v>99</v>
@@ -5539,21 +5542,21 @@
         <v>10</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L13" s="11">
         <v>2970</v>
@@ -5561,24 +5564,24 @@
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q13" s="13"/>
       <c r="R13" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
     </row>
     <row r="14" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C14" s="9">
         <v>99</v>
@@ -5587,50 +5590,50 @@
         <v>11</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L14" s="11">
         <v>2970</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q14" s="13"/>
       <c r="R14" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="S14" s="13"/>
       <c r="T14" s="13"/>
     </row>
     <row r="15" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C15" s="9">
         <v>99</v>
@@ -5639,52 +5642,52 @@
         <v>12</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L15" s="11">
         <v>6600</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S15" s="13"/>
       <c r="T15" s="13"/>
     </row>
     <row r="16" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C16" s="9">
         <v>99</v>
@@ -5694,53 +5697,53 @@
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L16" s="11">
         <v>5555</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="R16" s="12" t="s">
         <v>306</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="R16" s="12" t="s">
-        <v>305</v>
       </c>
       <c r="S16" s="13"/>
       <c r="T16" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C17" s="9">
         <v>99</v>
@@ -5749,48 +5752,48 @@
         <v>13</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L17" s="11">
         <v>7777</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q17" s="13"/>
       <c r="R17" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -5829,7 +5832,7 @@
         <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5837,7 +5840,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5845,7 +5848,7 @@
         <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5877,7 +5880,7 @@
         <v>1341</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5885,7 +5888,7 @@
         <v>1547</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5893,7 +5896,7 @@
         <v>1548</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5901,7 +5904,7 @@
         <v>1549</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5909,7 +5912,7 @@
         <v>1550</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5917,7 +5920,7 @@
         <v>1551</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5957,7 +5960,7 @@
         <v>3318</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5965,7 +5968,7 @@
         <v>3319</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5973,7 +5976,7 @@
         <v>3320</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5981,7 +5984,7 @@
         <v>3321</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5989,7 +5992,7 @@
         <v>3322</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5997,7 +6000,7 @@
         <v>3323</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6005,7 +6008,7 @@
         <v>3324</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6013,7 +6016,7 @@
         <v>3325</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6053,7 +6056,7 @@
         <v>3827</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6157,7 +6160,7 @@
         <v>6073</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6165,7 +6168,7 @@
         <v>6074</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6173,7 +6176,7 @@
         <v>6075</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6181,7 +6184,7 @@
         <v>6076</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6197,7 +6200,7 @@
         <v>6178</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6205,7 +6208,7 @@
         <v>6522</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6213,7 +6216,7 @@
         <v>6607</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6221,7 +6224,7 @@
         <v>6608</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6229,7 +6232,7 @@
         <v>6609</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6237,7 +6240,7 @@
         <v>6878</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6285,7 +6288,7 @@
         <v>7493</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6293,7 +6296,7 @@
         <v>8298</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6301,7 +6304,7 @@
         <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6309,7 +6312,7 @@
         <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6317,7 +6320,7 @@
         <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6325,7 +6328,7 @@
         <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6333,7 +6336,7 @@
         <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6341,7 +6344,7 @@
         <v>8728</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6365,7 +6368,7 @@
         <v>9534</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6429,7 +6432,7 @@
         <v>10513</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6437,7 +6440,7 @@
         <v>10514</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6445,7 +6448,7 @@
         <v>10515</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6453,7 +6456,7 @@
         <v>10516</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6461,7 +6464,7 @@
         <v>10517</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6469,7 +6472,7 @@
         <v>10518</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6485,7 +6488,7 @@
         <v>10520</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6493,7 +6496,7 @@
         <v>10521</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6533,7 +6536,7 @@
         <v>11108</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6541,7 +6544,7 @@
         <v>11119</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6549,7 +6552,7 @@
         <v>11196</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6557,7 +6560,7 @@
         <v>11207</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6565,7 +6568,7 @@
         <v>11552</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6573,7 +6576,7 @@
         <v>11556</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6581,7 +6584,7 @@
         <v>11559</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6589,7 +6592,7 @@
         <v>11562</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6597,7 +6600,7 @@
         <v>11565</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6605,7 +6608,7 @@
         <v>11568</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6613,7 +6616,7 @@
         <v>11588</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6621,7 +6624,7 @@
         <v>12257</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6629,7 +6632,7 @@
         <v>12258</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6637,7 +6640,7 @@
         <v>12261</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6685,7 +6688,7 @@
         <v>12863</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6693,7 +6696,7 @@
         <v>12864</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6701,7 +6704,7 @@
         <v>12865</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6709,7 +6712,7 @@
         <v>12866</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6717,7 +6720,7 @@
         <v>12869</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6725,7 +6728,7 @@
         <v>13055</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6733,7 +6736,7 @@
         <v>13056</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6741,7 +6744,7 @@
         <v>13057</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6749,7 +6752,7 @@
         <v>13060</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6757,7 +6760,7 @@
         <v>13295</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6765,7 +6768,7 @@
         <v>13381</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6773,7 +6776,7 @@
         <v>13382</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6781,7 +6784,7 @@
         <v>13383</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6789,7 +6792,7 @@
         <v>13384</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6962,7 +6965,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B143">
-    <sortCondition ref="A2:A143"/>
+    <sortCondition ref="A1:A143"/>
   </sortState>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6981,13 +6984,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -6995,10 +6998,10 @@
         <v>46264</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1567DDE9-D7D0-49A5-92DF-CC01CEFCA5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04C5C57-95D6-4B5B-95A1-07465A909A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>スーパ―ノエルドラゴン(×10),ニジピィ(×4),ぷれドラ(×2)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>べりドラ(×1)</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -2213,10 +2209,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>スーパ―ノエルドラゴン(×10)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>流星龍・メテオロン(×1),闇魔槍・デスピアード(×1),ダイヤドラゴンフルーツ(×1)</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -3102,10 +3094,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>レインボーメタルドラゴン(×1),スーパ―ノエルドラゴン(×5)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>潜在たまドラ☆神キラー,潜在たまドラ☆ドラゴンキラー,潜在たまドラ☆悪魔キラー,潜在たまドラ☆マシンキラー,潜在たまドラ☆バランスキラー,潜在たまドラ☆攻撃キラー,潜在たまドラ☆体力キラー,潜在たまドラ☆回復キラー(×5),潜在たまドラ☆スキルブースト++,潜在たまドラ☆アシスト無効回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍(×3)</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -3399,14 +3387,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>スーパ―ノエルドラゴン(×5)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>スーパ―ノエルドラゴン(×3)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>ゴールドたまドラ(×1～2),キングゴールドドラゴンズ(×1)</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -3743,6 +3723,26 @@
     <rPh sb="9" eb="10">
       <t>ミズ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×10)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×10),ニジピィ(×4),ぷれドラ(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レインボーメタルドラゴン(×1),スーパーノエルドラゴン(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×3)</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -4891,40 +4891,40 @@
         <v>8</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>107</v>
-      </c>
       <c r="J1" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>11</v>
@@ -4939,7 +4939,7 @@
         <v>13</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -4956,29 +4956,29 @@
         <v>12</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L2" s="11">
         <v>2970</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N2" s="11"/>
       <c r="O2" s="12" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P2" s="13"/>
       <c r="Q2" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R2" s="12" t="s">
         <v>14</v>
@@ -5008,29 +5008,29 @@
         <v>15</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L3" s="11">
         <v>2970</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="12" t="s">
@@ -5053,7 +5053,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="9">
         <v>99</v>
@@ -5062,39 +5062,39 @@
         <v>12</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="15" t="s">
         <v>115</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>116</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L4" s="11">
         <v>2970</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N4" s="11"/>
       <c r="O4" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P4" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q4" s="12" t="s">
         <v>19</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>20</v>
       </c>
       <c r="R4" s="13"/>
       <c r="S4" s="13"/>
@@ -5114,46 +5114,46 @@
         <v>15</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L5" s="11">
         <v>6666</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="R5" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="Q5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="S5" s="13"/>
       <c r="T5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5170,56 +5170,56 @@
         <v>15</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L6" s="11">
         <v>2970</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N6" s="11">
         <v>30</v>
       </c>
       <c r="O6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" s="12" t="s">
         <v>23</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="R6" s="12" t="s">
-        <v>24</v>
       </c>
       <c r="S6" s="13"/>
       <c r="T6" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="C7" s="9">
         <v>99</v>
@@ -5229,20 +5229,20 @@
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G7" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="L7" s="11">
         <v>2970</v>
@@ -5250,28 +5250,28 @@
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="P7" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="R7" s="12" t="s">
-        <v>149</v>
-      </c>
       <c r="S7" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T7" s="13"/>
     </row>
     <row r="8" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" s="9">
         <v>99</v>
@@ -5281,20 +5281,20 @@
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="L8" s="11">
         <v>2970</v>
@@ -5302,28 +5302,28 @@
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="P8" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="Q8" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="R8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="Q8" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="R8" s="12" t="s">
-        <v>172</v>
-      </c>
       <c r="S8" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T8" s="13"/>
     </row>
     <row r="9" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="9">
         <v>99</v>
@@ -5333,20 +5333,20 @@
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G9" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>140</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>141</v>
       </c>
       <c r="L9" s="11">
         <v>7777</v>
@@ -5354,26 +5354,26 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q9" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="R9" s="12" t="s">
         <v>194</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="S9" s="13"/>
       <c r="T9" s="13"/>
     </row>
     <row r="10" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="9">
         <v>99</v>
@@ -5382,23 +5382,23 @@
         <v>14</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G10" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>142</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="L10" s="11">
         <v>5000</v>
@@ -5406,28 +5406,28 @@
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="R10" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="S10" s="12" t="s">
         <v>209</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="R10" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="S10" s="12" t="s">
-        <v>211</v>
       </c>
       <c r="T10" s="13"/>
     </row>
     <row r="11" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" s="9">
         <v>99</v>
@@ -5436,23 +5436,23 @@
         <v>15</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F11" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="L11" s="11">
         <v>9999</v>
@@ -5460,30 +5460,30 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q11" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="R11" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="T11" s="12" t="s">
         <v>221</v>
-      </c>
-      <c r="Q11" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="R11" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="S11" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="T11" s="12" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C12" s="9">
         <v>99</v>
@@ -5492,48 +5492,48 @@
         <v>9</v>
       </c>
       <c r="E12" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>239</v>
-      </c>
       <c r="G12" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L12" s="11">
         <v>2970</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="S12" s="13"/>
       <c r="T12" s="13"/>
     </row>
     <row r="13" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="C13" s="9">
         <v>99</v>
@@ -5542,21 +5542,21 @@
         <v>10</v>
       </c>
       <c r="E13" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>240</v>
-      </c>
       <c r="G13" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L13" s="11">
         <v>2970</v>
@@ -5564,24 +5564,24 @@
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Q13" s="13"/>
       <c r="R13" s="12" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
     </row>
     <row r="14" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C14" s="9">
         <v>99</v>
@@ -5590,50 +5590,50 @@
         <v>11</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L14" s="11">
         <v>2970</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="Q14" s="13"/>
       <c r="R14" s="12" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="S14" s="13"/>
       <c r="T14" s="13"/>
     </row>
     <row r="15" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C15" s="9">
         <v>99</v>
@@ -5642,52 +5642,52 @@
         <v>12</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>248</v>
-      </c>
       <c r="I15" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L15" s="11">
         <v>6600</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="12" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="12" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="S15" s="13"/>
       <c r="T15" s="13"/>
     </row>
     <row r="16" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C16" s="9">
         <v>99</v>
@@ -5697,53 +5697,53 @@
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="I16" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>252</v>
-      </c>
       <c r="J16" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="L16" s="11">
         <v>5555</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="12" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="R16" s="12" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="S16" s="13"/>
       <c r="T16" s="12" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C17" s="9">
         <v>99</v>
@@ -5752,48 +5752,48 @@
         <v>13</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L17" s="11">
         <v>7777</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="12" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="Q17" s="13"/>
       <c r="R17" s="12" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -5821,10 +5821,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5832,7 +5832,7 @@
         <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5840,7 +5840,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5848,7 +5848,7 @@
         <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5856,7 +5856,7 @@
         <v>1077</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5864,7 +5864,7 @@
         <v>1081</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5872,7 +5872,7 @@
         <v>1083</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5880,7 +5880,7 @@
         <v>1341</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5888,7 +5888,7 @@
         <v>1547</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5896,7 +5896,7 @@
         <v>1548</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5904,7 +5904,7 @@
         <v>1549</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5912,7 +5912,7 @@
         <v>1550</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5920,7 +5920,7 @@
         <v>1551</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5928,7 +5928,7 @@
         <v>1709</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5936,7 +5936,7 @@
         <v>2250</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5944,7 +5944,7 @@
         <v>2425</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5952,7 +5952,7 @@
         <v>3317</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5960,7 +5960,7 @@
         <v>3318</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5968,7 +5968,7 @@
         <v>3319</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5976,7 +5976,7 @@
         <v>3320</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5984,7 +5984,7 @@
         <v>3321</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -5992,7 +5992,7 @@
         <v>3322</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6000,7 +6000,7 @@
         <v>3323</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6008,7 +6008,7 @@
         <v>3324</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6016,7 +6016,7 @@
         <v>3325</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6024,7 +6024,7 @@
         <v>3700</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6032,7 +6032,7 @@
         <v>3701</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6040,7 +6040,7 @@
         <v>3702</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6048,7 +6048,7 @@
         <v>3795</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6056,7 +6056,7 @@
         <v>3827</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6064,7 +6064,7 @@
         <v>3891</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6072,7 +6072,7 @@
         <v>3911</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6080,7 +6080,7 @@
         <v>3971</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6088,7 +6088,7 @@
         <v>3973</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6096,7 +6096,7 @@
         <v>3974</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6104,7 +6104,7 @@
         <v>4014</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6112,7 +6112,7 @@
         <v>4369</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6120,7 +6120,7 @@
         <v>4370</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6128,7 +6128,7 @@
         <v>4371</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6136,7 +6136,7 @@
         <v>4372</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6144,7 +6144,7 @@
         <v>4373</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6152,7 +6152,7 @@
         <v>5739</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6160,7 +6160,7 @@
         <v>6073</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6168,7 +6168,7 @@
         <v>6074</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6176,7 +6176,7 @@
         <v>6075</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6184,7 +6184,7 @@
         <v>6076</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6192,7 +6192,7 @@
         <v>6077</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6200,7 +6200,7 @@
         <v>6178</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6208,7 +6208,7 @@
         <v>6522</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6216,7 +6216,7 @@
         <v>6607</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6224,7 +6224,7 @@
         <v>6608</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6232,7 +6232,7 @@
         <v>6609</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6240,7 +6240,7 @@
         <v>6878</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6248,7 +6248,7 @@
         <v>7020</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6256,7 +6256,7 @@
         <v>7021</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6264,7 +6264,7 @@
         <v>7022</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6272,7 +6272,7 @@
         <v>7023</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6280,7 +6280,7 @@
         <v>7042</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6288,7 +6288,7 @@
         <v>7493</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6296,7 +6296,7 @@
         <v>8298</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6304,7 +6304,7 @@
         <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6312,7 +6312,7 @@
         <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6320,7 +6320,7 @@
         <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6328,7 +6328,7 @@
         <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6336,7 +6336,7 @@
         <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6344,7 +6344,7 @@
         <v>8728</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6352,7 +6352,7 @@
         <v>9000</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6360,7 +6360,7 @@
         <v>9454</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6368,7 +6368,7 @@
         <v>9534</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6376,7 +6376,7 @@
         <v>10022</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6384,7 +6384,7 @@
         <v>10023</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6392,7 +6392,7 @@
         <v>10024</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6400,7 +6400,7 @@
         <v>10025</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6408,7 +6408,7 @@
         <v>10026</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6416,7 +6416,7 @@
         <v>10114</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6424,7 +6424,7 @@
         <v>10512</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6432,7 +6432,7 @@
         <v>10513</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6440,7 +6440,7 @@
         <v>10514</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6448,7 +6448,7 @@
         <v>10515</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6456,7 +6456,7 @@
         <v>10516</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6464,7 +6464,7 @@
         <v>10517</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6472,7 +6472,7 @@
         <v>10518</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6480,7 +6480,7 @@
         <v>10519</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6488,7 +6488,7 @@
         <v>10520</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6496,7 +6496,7 @@
         <v>10521</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6504,7 +6504,7 @@
         <v>10528</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6512,7 +6512,7 @@
         <v>10529</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6520,7 +6520,7 @@
         <v>10530</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6528,7 +6528,7 @@
         <v>10533</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6536,7 +6536,7 @@
         <v>11108</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6544,7 +6544,7 @@
         <v>11119</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6552,7 +6552,7 @@
         <v>11196</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6560,7 +6560,7 @@
         <v>11207</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6568,7 +6568,7 @@
         <v>11552</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6576,7 +6576,7 @@
         <v>11556</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6584,7 +6584,7 @@
         <v>11559</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6592,7 +6592,7 @@
         <v>11562</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6600,7 +6600,7 @@
         <v>11565</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6608,7 +6608,7 @@
         <v>11568</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6616,7 +6616,7 @@
         <v>11588</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6624,7 +6624,7 @@
         <v>12257</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6632,7 +6632,7 @@
         <v>12258</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6640,7 +6640,7 @@
         <v>12261</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6648,7 +6648,7 @@
         <v>12691</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6656,7 +6656,7 @@
         <v>12692</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6664,7 +6664,7 @@
         <v>12693</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6672,7 +6672,7 @@
         <v>12696</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6680,7 +6680,7 @@
         <v>12697</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6688,7 +6688,7 @@
         <v>12863</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6696,7 +6696,7 @@
         <v>12864</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6704,7 +6704,7 @@
         <v>12865</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6712,7 +6712,7 @@
         <v>12866</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6720,7 +6720,7 @@
         <v>12869</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6728,7 +6728,7 @@
         <v>13055</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6736,7 +6736,7 @@
         <v>13056</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6744,7 +6744,7 @@
         <v>13057</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6752,7 +6752,7 @@
         <v>13060</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6760,7 +6760,7 @@
         <v>13295</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6768,7 +6768,7 @@
         <v>13381</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6776,7 +6776,7 @@
         <v>13382</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6784,7 +6784,7 @@
         <v>13383</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6792,7 +6792,7 @@
         <v>13384</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6800,7 +6800,7 @@
         <v>13499</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6808,7 +6808,7 @@
         <v>13500</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6816,7 +6816,7 @@
         <v>13501</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6824,7 +6824,7 @@
         <v>13503</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6832,7 +6832,7 @@
         <v>13590</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6840,7 +6840,7 @@
         <v>13591</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6848,7 +6848,7 @@
         <v>13592</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6856,7 +6856,7 @@
         <v>13594</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6864,7 +6864,7 @@
         <v>13667</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6872,7 +6872,7 @@
         <v>13799</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6880,7 +6880,7 @@
         <v>13800</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6888,7 +6888,7 @@
         <v>13801</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6896,7 +6896,7 @@
         <v>13803</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6904,7 +6904,7 @@
         <v>13821</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6912,7 +6912,7 @@
         <v>13822</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6920,7 +6920,7 @@
         <v>13823</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6928,7 +6928,7 @@
         <v>13825</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6936,7 +6936,7 @@
         <v>14023</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6944,7 +6944,7 @@
         <v>14024</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6952,7 +6952,7 @@
         <v>14025</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6960,7 +6960,7 @@
         <v>14027</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -6984,13 +6984,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" t="s">
         <v>225</v>
       </c>
-      <c r="B1" t="s">
-        <v>227</v>
-      </c>
       <c r="C1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -6998,10 +6998,10 @@
         <v>46264</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04C5C57-95D6-4B5B-95A1-07465A909A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E302C1-226F-495F-8BED-E437F7639A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -3395,68 +3395,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>煌窮の億兆龍・アグリゲートの希石,冥窮の億兆龍・アグリゲートの希石,緋窮の億兆龍・アグリゲートの希石, 蒼窮の億兆龍・アグリゲートの希石,翠窮の億兆龍・アグリゲートの希石(×4(※1))</t>
-    <rPh sb="14" eb="15">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="83" eb="84">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>セキ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>※1ランダム1色が4個ドロップする。その内訳は、ボス本体×1 + ボス部位×3。,※2確率ドロップのゴールドたまドラ、キングゴールドドラゴンズのドロップ数で増減する？</t>
-    <rPh sb="7" eb="8">
-      <t>ショク</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ウチワケ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ホンタイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ブイ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="76" eb="77">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>ゾウゲン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>暴乱の極悪生命体・ゴクレグスの希石</t>
     <rPh sb="0" eb="2">
       <t>ボウラン</t>
@@ -3743,6 +3681,62 @@
   </si>
   <si>
     <t>スーパーノエルドラゴン(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煌窮の億兆龍・アグリゲートの希石,冥窮の億兆龍・アグリゲートの希石,緋窮の億兆龍・アグリゲートの希石, 蒼窮の億兆龍・アグリゲートの希石,翠窮の億兆龍・アグリゲートの希石(×4(ボス本体・部位(※1)))</t>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※1ランダム1色が4個ドロップする。※2確率ドロップのゴールドたまドラ、キングゴールドドラゴンズのドロップ数で増減する？</t>
+    <rPh sb="7" eb="8">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ゾウゲン</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -4924,7 +4918,7 @@
         <v>37</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>11</v>
@@ -5091,7 +5085,7 @@
         <v>26</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>19</v>
@@ -5357,7 +5351,7 @@
         <v>192</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q9" s="12" t="s">
         <v>193</v>
@@ -5571,7 +5565,7 @@
       </c>
       <c r="Q13" s="13"/>
       <c r="R13" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
@@ -5619,7 +5613,7 @@
         <v>276</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q14" s="13"/>
       <c r="R14" s="12" t="s">
@@ -5673,7 +5667,7 @@
         <v>289</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="12" t="s">
@@ -5722,10 +5716,10 @@
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="12" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q16" s="12" t="s">
         <v>300</v>
@@ -5735,7 +5729,7 @@
       </c>
       <c r="S16" s="13"/>
       <c r="T16" s="12" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5767,10 +5761,10 @@
         <v>252</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L17" s="11">
         <v>7777</v>
@@ -5780,20 +5774,20 @@
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q17" s="13"/>
       <c r="R17" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="T17" s="12" t="s">
         <v>310</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="T17" s="12" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -6304,7 +6298,7 @@
         <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6312,7 +6306,7 @@
         <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6320,7 +6314,7 @@
         <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6328,7 +6322,7 @@
         <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6336,7 +6330,7 @@
         <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6624,7 +6618,7 @@
         <v>12257</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6632,7 +6626,7 @@
         <v>12258</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -6640,7 +6634,7 @@
         <v>12261</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E302C1-226F-495F-8BED-E437F7639A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCD6777-B782-4528-B4EA-4DAD2534FDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -3684,43 +3684,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>煌窮の億兆龍・アグリゲートの希石,冥窮の億兆龍・アグリゲートの希石,緋窮の億兆龍・アグリゲートの希石, 蒼窮の億兆龍・アグリゲートの希石,翠窮の億兆龍・アグリゲートの希石(×4(ボス本体・部位(※1)))</t>
-    <rPh sb="14" eb="15">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="83" eb="84">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>ホンタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>※1ランダム1色が4個ドロップする。※2確率ドロップのゴールドたまドラ、キングゴールドドラゴンズのドロップ数で増減する？</t>
     <rPh sb="7" eb="8">
       <t>ショク</t>
@@ -3736,6 +3699,43 @@
     </rPh>
     <rPh sb="55" eb="57">
       <t>ゾウゲン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煌窮の億兆龍・アグリゲートの希石,冥窮の億兆龍・アグリゲートの希石,緋窮の億兆龍・アグリゲートの希石, 蒼窮の億兆龍・アグリゲートの希石,翠窮の億兆龍・アグリゲートの希石(×4 (ボス本体・部位(※1)))</t>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>ホンタイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -4407,7 +4407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4476,9 +4476,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -5716,7 +5713,7 @@
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P16" s="12" t="s">
         <v>323</v>
@@ -5729,7 +5726,7 @@
       </c>
       <c r="S16" s="13"/>
       <c r="T16" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5746,7 +5743,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>235</v>
+        <v>108</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>242</v>
@@ -6662,10 +6659,10 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="22">
+      <c r="A107" s="3">
         <v>12696</v>
       </c>
-      <c r="B107" s="22" t="s">
+      <c r="B107" s="3" t="s">
         <v>167</v>
       </c>
     </row>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCD6777-B782-4528-B4EA-4DAD2534FDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B3C9F8-A7C2-41C6-BC94-BA5F87F99AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="514">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -3739,6 +3739,1880 @@
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>未知の新星</t>
+    <rPh sb="0" eb="2">
+      <t>ミチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>業炎の百龍</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>4,000万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/50</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陰</t>
+    <rPh sb="0" eb="1">
+      <t>イン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼穹の千龍</t>
+    <rPh sb="0" eb="2">
+      <t>ソウキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/80</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>4,500万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>20億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>永刻の万龍</t>
+    <rPh sb="0" eb="2">
+      <t>エイコク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>陽</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>5,000万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>25億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潰滅の兆龍</t>
+    <rPh sb="0" eb="1">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>メツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/200</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>5,500万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>30億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>混沌の億兆龍</t>
+    <rPh sb="0" eb="2">
+      <t>コントン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オクチョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/100</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/4</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>6,000万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>20億～40億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極悪生命体</t>
+    <rPh sb="0" eb="5">
+      <t>ゴクアクセイメイタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1億</t>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>45億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏業炎の百龍</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/500</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏蒼穹の千龍</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/250</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>5,800万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏永刻の万龍</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>エイコク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/400</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>35億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏潰滅の兆龍</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>6,500万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>37億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏混沌の億兆龍</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コントン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>7,000万</t>
+    <rPh sb="5" eb="6">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>35億～45億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏極悪生命体</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="1" eb="6">
+      <t>ゴクアクセイメイタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/1000</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.5億</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>3億</t>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>封印されし百式龍</t>
+    <rPh sb="0" eb="2">
+      <t>フウイン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒャクシキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>百式龍・ビャクレンコウの希石</t>
+    <rPh sb="0" eb="2">
+      <t>ヒャクシキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>封印されし百式龍,百式龍・ビャクレンコウの希石(ボス本体)</t>
+    <rPh sb="26" eb="28">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キングたまドラ(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極醒の神葬狼・フェンリル=ヴィズの希石</t>
+    <rPh sb="0" eb="1">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極醒の威女神・カーリーの希石</t>
+    <rPh sb="0" eb="1">
+      <t>キョク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極醒の天陽神・アテンの希石</t>
+    <rPh sb="0" eb="2">
+      <t>キョクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極醒の霊央神・カミムスビの希石</t>
+    <rPh sb="0" eb="2">
+      <t>キョクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極醒の神葬狼・フェンリル=ヴィズの希石,極醒の威女神・カーリーの希石,極醒の天陽神・アテンの希石,極醒の霊央神・カミムスビの希石(×1),潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×4)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>瞑想せし千手龍</t>
+    <rPh sb="0" eb="2">
+      <t>メイソウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センテ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>千手龍・センキョウの希石</t>
+    <rPh sb="0" eb="2">
+      <t>センテ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>瞑想せし千手龍,千手龍・センキョウの希石(ボス本体)</t>
+    <rPh sb="23" eb="25">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×3),潜在たまドラ☆スキル遅延耐性(×8)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ,ニジピィ(×3),潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×1)</t>
+    <rPh sb="178" eb="179">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太古に刻まれし万寿龍</t>
+    <rPh sb="0" eb="2">
+      <t>タイコ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キザ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>マンジュ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>リュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>万寿龍・クーバンシェンの希石</t>
+    <rPh sb="0" eb="3">
+      <t>マンジュリュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太古に刻まれし万寿龍,万寿龍・クーバンシェンの希石(ボス本体)</t>
+    <rPh sb="28" eb="30">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×10)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>封印されし凶兆</t>
+    <rPh sb="0" eb="2">
+      <t>フウイン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>凶兆龍・ゼンチョウガの希石</t>
+    <rPh sb="0" eb="2">
+      <t>キョウチョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>封印されし凶兆,凶兆龍・ゼンチョウガの希石(ボス本体)</t>
+    <rPh sb="24" eb="26">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レインボーメタルドラゴン(×10)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆HP強化++,潜在たまドラ☆攻撃強化++,潜在たまドラ☆回復強化++(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼炎星・イフリート</t>
+    <rPh sb="0" eb="1">
+      <t>アオイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>碧炎星・イフリート</t>
+    <rPh sb="0" eb="1">
+      <t>ヘキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>輝炎星・イフリート</t>
+    <rPh sb="0" eb="1">
+      <t>カガヤ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ホノオホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>黒炎星・イフリート</t>
+    <rPh sb="0" eb="1">
+      <t>コク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎天双極星・イフリート</t>
+    <rPh sb="0" eb="2">
+      <t>エンテン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅氷星・リヴァイアサン</t>
+    <rPh sb="0" eb="1">
+      <t>ベニ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>碧氷星・リヴァイアサン</t>
+    <rPh sb="0" eb="1">
+      <t>ヘキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>輝氷星・リヴァイアサン</t>
+    <rPh sb="0" eb="1">
+      <t>カガヤ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コオリホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>黒氷星・リヴァイアサン</t>
+    <rPh sb="0" eb="1">
+      <t>コク</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コオリホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水天双極星・リヴァイアサン</t>
+    <rPh sb="0" eb="2">
+      <t>スイテン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅樹星・ファフニール</t>
+    <rPh sb="0" eb="1">
+      <t>ベニ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ジュ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼樹星・ファフニール</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ジュ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>輝樹星・ファフニール</t>
+    <rPh sb="0" eb="1">
+      <t>カガヤ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ジュホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>黒樹星・ファフニール</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ジュホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風天双極星・ファフニール</t>
+    <rPh sb="0" eb="1">
+      <t>フウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅光星・神龍</t>
+    <rPh sb="0" eb="1">
+      <t>ベニ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼光星・神龍</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>碧光星・神龍</t>
+    <rPh sb="0" eb="1">
+      <t>ヘキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ヒカリホシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>黒光星・神龍</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ヒカリホシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>光天双極星・神龍</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シンリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅闇星・ティアマット</t>
+    <rPh sb="0" eb="1">
+      <t>ベニ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼闇星・ティアマット</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>碧闇星・ティアマット</t>
+    <rPh sb="0" eb="1">
+      <t>ヘキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>闇天双極星・ティアマット</t>
+    <rPh sb="0" eb="1">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>輝闇星・ティアマット</t>
+    <rPh sb="0" eb="1">
+      <t>カガヤ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ソウセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>蒼炎星・イフリート,碧炎星・イフリート,輝炎星・イフリート,黒炎星・イフリート,炎天双極星・イフリート,紅氷星・リヴァイアサン,碧氷星・リヴァイアサン,輝氷星・リヴァイアサン,黒氷星・リヴァイアサン,水天双極星・リヴァイアサン,紅樹星・ファフニール,蒼樹星・ファフニール,輝樹星・ファフニール,黒樹星・ファフニール,風天双極星・ファフニール,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>紅光星・神龍,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>蒼光星・神龍,碧光星・神龍,黒光星・神龍,光天双極星・神龍,紅闇星・ティアマット,蒼闇星・ティアマット,碧闇星・ティアマット,輝闇星・ティアマット,闇天双極星・ティアマット(ボス本体(25体からランダム1つ))</t>
+    </r>
+    <rPh sb="267" eb="269">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="272" eb="273">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×5),潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極悪生命体・ゴクレグスの希石</t>
+    <rPh sb="0" eb="5">
+      <t>ゴクアクセイメイタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超ホーリードラゴンの希石</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超デビルドラゴンの希石</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超白龍の希石</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ハクリュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超バジリスクの希石</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極悪生命体・ゴクレグスの希石(ボス本体)</t>
+    <rPh sb="17" eb="19">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超白龍の希石,超バジリスクの希石(×1),潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×11～12)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超ホーリードラゴンの希石,超デビルドラゴンの希石(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極醒の神葬狼・フェンリル=ヴィズの希石,極醒の威女神・カーリーの希石,極醒の天陽神・アテンの希石,極醒の霊央神・カミムスビの希石(×1),ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ(×3),潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×4)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×3),ニジピィ(×3),潜在たまドラ☆スキル遅延耐性(×4)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4),潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キングたまドラ(×5),スーパーノエルドラゴン(×10)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>封印されし凶兆,凶兆龍・ゼンチョウガの希石(ボス本体)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>リッチゴールドドラゴン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>リッチゴールドドラゴン(×6),レインボーメタルドラゴン(×10)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆HP強化++,潜在たまドラ☆攻撃強化++,潜在たまドラ☆回復強化++(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼炎星・イフリート,碧炎星・イフリート,輝炎星・イフリート,黒炎星・イフリート,炎天双極星・イフリート,紅氷星・リヴァイアサン,碧氷星・リヴァイアサン,輝氷星・リヴァイアサン,黒氷星・リヴァイアサン,水天双極星・リヴァイアサン,紅樹星・ファフニール,蒼樹星・ファフニール,輝樹星・ファフニール,黒樹星・ファフニール,風天双極星・ファフニール,紅光星・神龍,蒼光星・神龍,碧光星・神龍,黒光星・神龍,光天双極星・神龍,紅闇星・ティアマット,蒼闇星・ティアマット,碧闇星・ティアマット,輝闇星・ティアマット,闇天双極星・ティアマット(ボス本体(25体からランダム1つ))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ホノピィ,ミズピィ,モクピィ,ヒカピィ,ヤミピィ(×5),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×5),潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極悪生命体・ゴクレグスの希石(ボス本体)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>超白龍の希石,超バジリスクの希石(×1),潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×12)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級1人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>未知の新星ラッシュ</t>
+    <rPh sb="0" eb="2">
+      <t>ミチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シンセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏未知の新星ラッシュ</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ミチ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>契約の天使</t>
+    <rPh sb="0" eb="2">
+      <t>ケイヤク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テンシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>銀翼の白迅帝</t>
+    <rPh sb="0" eb="2">
+      <t>ギンヨク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ピクセルスプライツ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>天境の白霹竜</t>
+    <rPh sb="0" eb="2">
+      <t>テンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>冥境の黒熾龍</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/2000</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【リーダーチェンジ無効】,※ゲリラ時のみで常設時は効果を受けない。</t>
+  </si>
+  <si>
+    <t>【リーダーチェンジ無効】,※ゲリラ時のみで常設時は効果を受けない。</t>
+    <rPh sb="9" eb="11">
+      <t>ムコウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジョウセツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1億(ゲリラ時：10億)</t>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.1億(ゲリラ時：11億)</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10"万"</t>
+    <rPh sb="3" eb="4">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11"万"</t>
+    <rPh sb="3" eb="4">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>39～45</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アームズシーカー：20周</t>
+    <rPh sb="11" eb="12">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【リーダーチェンジ無効】,※ゲリラ時のみで常設時は効果を受けない。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.2億(ゲリラ時：12億)</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>12億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>モリりんのカード：20周,ワルりんのカード：20周,龍現門(アグリゲート)：約550周,(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低495周))</t>
+    <rPh sb="11" eb="12">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>龍現門(アグリゲート)：約550周,(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低495周))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゴクレグス：約230周,(※表示している値は平均をとったも。超デビルドラゴンの希石の偏りによってレートが増減する。(最低99周))</t>
+    <rPh sb="6" eb="7">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヘイキン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>カタヨ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ゾウゲン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>サイテイ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>龍現門(アグリゲート)：約550周,(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低495周))</t>
+    <rPh sb="0" eb="1">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘイキン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>カタヨ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ゾウゲン</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>サイテイ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・アテナ：約8周,ドット・魔王・ヴァンパイアロード：約8周,※これは交換ではなく、ドット進化に必要なレートを示す。希石の偏りによってレートが増減する。</t>
+    <rPh sb="8" eb="9">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>マオウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>コウカン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シンカ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>カタヨ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ゾウゲン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>巴御前の強弓：10周,巴御前の薙刀：10周,合計で20周</t>
+    <rPh sb="0" eb="1">
+      <t>トモエ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ゴゼン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>トモエゴゼン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カタナ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/2</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.3億(ゲリラ時：13億)</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミゲイルの岩砕鎚：30周,ミゲイルの冥堕鎚：30周</t>
+    <rPh sb="5" eb="6">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>クダ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1/5000</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.4億(ゲリラ時：14億)</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>14億</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※ボスも含め、全体的に非確定ドロップで、安定した数に定まらないので、ドロップ数は目安として記載。</t>
+  </si>
+  <si>
+    <t>※ボスも含め、全体的に非確定ドロップで、安定した数に定まらないので、ドロップ数は目安として記載。</t>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ゼンタイテキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒカクテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>アンテイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>サダ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>メヤス</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎天双極星・イフリート,水天双極星・リヴァイアサン,風天双極星・ファフニール,光天双極星・神龍,闇天双極星・ティアマット(ボス本体(5体からランダム1つ))</t>
+    <rPh sb="63" eb="65">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×3～4),ニジピィ(×3～4),潜在たまドラ☆スキル遅延耐性(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>封印されし百式龍,百式龍・ビャクレンコウの希石(ボス本体)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>瞑想せし千手龍,千手龍・センキョウの希石(ボス本体)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太古に刻まれし万寿龍,万寿龍・クーバンシェンの希石(ボス本体)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×1～2),潜在たまドラ☆神キラー,潜在たまドラ☆ドラゴンキラー,潜在たまドラ☆悪魔キラー,潜在たまドラ☆マシンキラー,潜在たまドラ☆バランスキラー,潜在たまドラ☆攻撃キラー,潜在たまドラ☆体力キラー,潜在たまドラ☆回復キラー(×1～2),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×0～2),封印されし百式龍,百式龍・ビャクレンコウの希石(×1),瞑想せし千手龍,千手龍・センキョウの希石(×1),太古に刻まれし万寿龍,万寿龍・クーバンシェンの希石(×1),封印されし凶兆,凶兆龍・ゼンチョウガの希石(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎天双極星・イフリート,水天双極星・リヴァイアサン,風天双極星・ファフニール,光天双極星・神龍,闇天双極星・ティアマット(ボス本体(5体からランダム1つ)),ルウのおとも・モリりんの希石(乱入部位),ルウのおとも・ワルりんの希石(乱入部位)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×3),ニジピィ(×3),潜在たまドラ☆スキル遅延耐性(×3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゴールドたまドラ(×1)</t>
+  </si>
+  <si>
+    <t>極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×1),潜在たまドラ☆神キラー,潜在たまドラ☆ドラゴンキラー,潜在たまドラ☆悪魔キラー,潜在たまドラ☆マシンキラー,潜在たまドラ☆バランスキラー,潜在たまドラ☆攻撃キラー,潜在たまドラ☆体力キラー,潜在たまドラ☆回復キラー(×2),封印されし百式龍,百式龍・ビャクレンコウの希石(×1),瞑想せし千手龍,千手龍・センキョウの希石(×1),太古に刻まれし万寿龍,万寿龍・クーバンシェンの希石(×1),封印されし凶兆,凶兆龍・ゼンチョウガの希石(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×2～4),ニジピィ(×2～4),潜在たまドラ☆スキル遅延耐性(×2～3)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×1～3),潜在たまドラ☆アシスト無効回復,潜在たまドラ☆リーダーチェンジ耐性,潜在たまドラ☆お邪魔目覚め耐性,潜在たまドラ☆毒目覚め耐性,潜在たまドラ☆ダメージ無効貫通,潜在たまドラ☆属性吸収貫通,潜在たまドラ☆雲・操作不可回復,潜在たまドラ☆消せないドロップ回復,潜在たまドラ☆ダメージ上限解放,潜在たまドラ☆ダメージ上限解放8倍,潜在たまドラ☆スキルブースト++,潜在たまドラ☆ダメージ吸収貫通(×1～2),潜在たまドラ☆神キラー,潜在たまドラ☆ドラゴンキラー,潜在たまドラ☆悪魔キラー,潜在たまドラ☆マシンキラー,潜在たまドラ☆バランスキラー,潜在たまドラ☆攻撃キラー,潜在たまドラ☆体力キラー,潜在たまドラ☆回復キラー(×1～2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ディープシーカーの左腕の希石(6F部位),ディープシーカーの右腕の希石(6F部位)</t>
+  </si>
+  <si>
+    <t>キングたまドラ(×2),スーパーノエルドラゴン(×2),ニジピィ(×2),潜在たまドラ☆スキル遅延耐性(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆HP強化++,潜在たまドラ☆攻撃強化++,潜在たまドラ☆回復強化++(×4),潜在たまドラ☆神キラー,潜在たまドラ☆ドラゴンキラー,潜在たまドラ☆悪魔キラー,潜在たまドラ☆マシンキラー,潜在たまドラ☆バランスキラー,潜在たまドラ☆攻撃キラー,潜在たまドラ☆体力キラー,潜在たまドラ☆回復キラー(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※全体的に非確定ドロップである。(上記は最大ドロップ数を示す。)</t>
+  </si>
+  <si>
+    <t>※全体的に非確定ドロップである。(上記は最大ドロップ数を示す。)</t>
+    <rPh sb="1" eb="4">
+      <t>ゼンタイテキ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ヒカクテイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>シメ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・アテナの希石</t>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・魔王・ヴァンパイアロードの希石</t>
+    <rPh sb="4" eb="6">
+      <t>マオウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・アテナの希石,ドット・魔王・ヴァンパイアロードの希石(ボス本体(どちらか1体がドロップ))</t>
+    <rPh sb="33" eb="35">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドットリット</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×2),ニジピィ(×3),潜在たまドラ☆スキル遅延耐性(×7),ドットリット(×2),潜在たまドラ☆枠解放(×7)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※全体的に非確定ドロップである。(上記は最大ドロップ数を示す。)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>巴御前の希石(6F部位)</t>
+    <rPh sb="0" eb="3">
+      <t>トモエゴゼン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火の宝玉</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウギョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水の宝玉</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウギョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木の宝玉</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウギョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>光の宝玉</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウギョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>闇の宝玉</t>
+    <rPh sb="0" eb="1">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウギョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>創装の宝玉,火の宝玉,水の宝玉,木の宝玉,光の宝玉,闇の宝玉(×11),極キングルビードラゴン,極キングサファイアドラゴン,極キングエメラルドドラゴン,極キングゴールドドラゴン,極キングメタルドラゴン(×6)</t>
+    <rPh sb="6" eb="7">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウギョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホウギョク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホウギョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ホウギョク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホウギョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミゲイルの岩砕鎚の希石(4F部位),ミゲイルの冥堕鎚の希石(4F部位)</t>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ブイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ブイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーパーノエルドラゴン(×5),ニジピィ(×3),潜在たまドラ☆スキル遅延耐性(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サゲピィ,とじたまドラ,モドリット(×2)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミゲイルの岩砕鎚の希石</t>
+  </si>
+  <si>
+    <t>ミゲイルの冥堕鎚の希石</t>
+  </si>
 </sst>
 </file>
 
@@ -3747,7 +5621,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3915,6 +5789,15 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -4407,7 +6290,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4476,6 +6359,12 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -4853,19 +6742,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="18.58203125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="10.58203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" style="17" customWidth="1"/>
+    <col min="1" max="2" width="20.58203125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="10.58203125" style="17" customWidth="1"/>
     <col min="6" max="6" width="156.4140625" style="17" customWidth="1"/>
     <col min="7" max="8" width="30.58203125" style="18" customWidth="1"/>
     <col min="9" max="9" width="75.58203125" style="17" customWidth="1"/>
     <col min="10" max="14" width="25.58203125" style="17" customWidth="1"/>
     <col min="15" max="15" width="163.75" style="16" customWidth="1"/>
     <col min="16" max="16" width="71.1640625" style="16" customWidth="1"/>
-    <col min="17" max="17" width="69.08203125" style="16" customWidth="1"/>
+    <col min="17" max="17" width="71.08203125" style="16" customWidth="1"/>
     <col min="18" max="18" width="255.5" style="16" customWidth="1"/>
     <col min="19" max="19" width="151.1640625" style="16" customWidth="1"/>
     <col min="20" max="20" width="104.1640625" style="16" customWidth="1"/>
@@ -4878,10 +6766,10 @@
       <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -5787,13 +7675,904 @@
         <v>310</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" spans="1:20" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="18" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C18" s="9">
+        <v>99</v>
+      </c>
+      <c r="D18" s="9">
+        <v>16</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="L18" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+    </row>
+    <row r="19" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C19" s="9">
+        <v>99</v>
+      </c>
+      <c r="D19" s="9">
+        <v>16</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+    </row>
+    <row r="20" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C20" s="9">
+        <v>99</v>
+      </c>
+      <c r="D20" s="9">
+        <v>15</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H20" s="10"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+    </row>
+    <row r="21" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" s="9">
+        <v>99</v>
+      </c>
+      <c r="D21" s="9">
+        <v>16</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="H21" s="10"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="L21" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+    </row>
+    <row r="22" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C22" s="9">
+        <v>99</v>
+      </c>
+      <c r="D22" s="9">
+        <v>16</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="L22" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+    </row>
+    <row r="23" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C23" s="9">
+        <v>99</v>
+      </c>
+      <c r="D23" s="9">
+        <v>15</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="L23" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="S23" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="T23" s="13"/>
+    </row>
+    <row r="24" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C24" s="9">
+        <v>99</v>
+      </c>
+      <c r="D24" s="9">
+        <v>16</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="L24" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+    </row>
+    <row r="25" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C25" s="9">
+        <v>99</v>
+      </c>
+      <c r="D25" s="9">
+        <v>16</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="L25" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="S25" s="13"/>
+      <c r="T25" s="13"/>
+    </row>
+    <row r="26" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C26" s="9">
+        <v>99</v>
+      </c>
+      <c r="D26" s="9">
+        <v>15</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="L26" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
+    </row>
+    <row r="27" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C27" s="9">
+        <v>99</v>
+      </c>
+      <c r="D27" s="9">
+        <v>16</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="L27" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+    </row>
+    <row r="28" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" s="9">
+        <v>99</v>
+      </c>
+      <c r="D28" s="9">
+        <v>16</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="L28" s="11">
+        <v>2970</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="N28" s="9"/>
+      <c r="O28" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
+    </row>
+    <row r="29" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C29" s="9">
+        <v>99</v>
+      </c>
+      <c r="D29" s="9">
+        <v>15</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H29" s="10"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="L29" s="11">
+        <v>7777</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="N29" s="9"/>
+      <c r="O29" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="S29" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="T29" s="13"/>
+    </row>
+    <row r="30" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C30" s="9">
+        <v>99</v>
+      </c>
+      <c r="D30" s="9">
+        <v>15</v>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="H30" s="10"/>
+      <c r="I30" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="N30" s="9"/>
+      <c r="O30" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="R30" s="13"/>
+      <c r="S30" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="T30" s="12" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C31" s="9">
+        <v>99</v>
+      </c>
+      <c r="D31" s="9">
+        <v>15</v>
+      </c>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="N31" s="9"/>
+      <c r="O31" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q31" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="R31" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="S31" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="T31" s="13"/>
+    </row>
+    <row r="32" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C32" s="9">
+        <v>99</v>
+      </c>
+      <c r="D32" s="9">
+        <v>15</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="H32" s="10"/>
+      <c r="I32" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="O32" s="23"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="R32" s="13"/>
+      <c r="S32" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="T32" s="12" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C33" s="9">
+        <v>99</v>
+      </c>
+      <c r="D33" s="9">
+        <v>16</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="H33" s="10"/>
+      <c r="I33" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9">
+        <v>30</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="R33" s="13"/>
+      <c r="S33" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="T33" s="12" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C34" s="9">
+        <v>99</v>
+      </c>
+      <c r="D34" s="9">
+        <v>15</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="12" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C35" s="9">
+        <v>99</v>
+      </c>
+      <c r="D35" s="9">
+        <v>15</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="T35" s="12" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="C36" s="9">
+        <v>99</v>
+      </c>
+      <c r="D36" s="9">
+        <v>15</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="H36" s="10"/>
+      <c r="I36" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9">
+        <v>30</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="R36" s="13"/>
+      <c r="S36" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="T36" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5803,7 +8582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B143"/>
+  <dimension ref="A1:B196"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -6952,6 +9731,430 @@
       </c>
       <c r="B143" s="3" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" s="3">
+        <v>8914</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" s="3">
+        <v>8916</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" s="3">
+        <v>7680</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" s="3">
+        <v>7681</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" s="3">
+        <v>7684</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" s="3">
+        <v>7686</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" s="3">
+        <v>9227</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" s="3">
+        <v>9229</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" s="3">
+        <v>9455</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" s="3">
+        <v>9457</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" s="3">
+        <v>9716</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A155" s="3">
+        <v>9727</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" s="3">
+        <v>322</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" s="3">
+        <v>323</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" s="3">
+        <v>324</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" s="3">
+        <v>325</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" s="3">
+        <v>1109</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" s="3">
+        <v>326</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" s="3">
+        <v>327</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" s="3">
+        <v>328</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" s="3">
+        <v>329</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" s="3">
+        <v>1095</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" s="3">
+        <v>330</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" s="3">
+        <v>331</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A168" s="3">
+        <v>332</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A169" s="3">
+        <v>333</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" s="3">
+        <v>1096</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A171" s="3">
+        <v>334</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A172" s="3">
+        <v>335</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A173" s="3">
+        <v>336</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A174" s="3">
+        <v>337</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A175" s="3">
+        <v>1110</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A176" s="3">
+        <v>338</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A177" s="3">
+        <v>339</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A178" s="3">
+        <v>340</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" s="3">
+        <v>341</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" s="3">
+        <v>1111</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" s="3">
+        <v>11046</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A182" s="3">
+        <v>11039</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A183" s="3">
+        <v>11040</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A184" s="3">
+        <v>11037</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A185" s="3">
+        <v>11038</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A186" s="3">
+        <v>1340</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A187" s="3">
+        <v>13047</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A188" s="3">
+        <v>13048</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A189" s="3">
+        <v>3826</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A190" s="3">
+        <v>1325</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A191" s="3">
+        <v>1326</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A192" s="3">
+        <v>1327</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A193" s="3">
+        <v>1328</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A194" s="3">
+        <v>1329</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A195" s="3">
+        <v>13303</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A196" s="3">
+        <v>13304</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B3C9F8-A7C2-41C6-BC94-BA5F87F99AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C98778D-4758-42B1-AAC6-91EA9EFBD8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="517">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5612,6 +5612,39 @@
   </si>
   <si>
     <t>ミゲイルの冥堕鎚の希石</t>
+  </si>
+  <si>
+    <t>ルウのおとも・モリりんの希石</t>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ルウのおとも・ワルりんの希石</t>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>巴御前の希石</t>
+    <rPh sb="0" eb="3">
+      <t>トモエゴゼン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
@@ -6290,7 +6323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6362,9 +6395,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -8362,7 +8392,7 @@
       <c r="N32" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="O32" s="23"/>
+      <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="12" t="s">
         <v>489</v>
@@ -8582,7 +8612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B196"/>
+  <dimension ref="A1:B199"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -10155,6 +10185,30 @@
       </c>
       <c r="B196" s="3" t="s">
         <v>513</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A197" s="3">
+        <v>12345</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A198" s="3">
+        <v>12346</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A199" s="3">
+        <v>12114</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C98778D-4758-42B1-AAC6-91EA9EFBD8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABAC851-D4DB-4593-8D92-718927A37A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="519">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5643,6 +5643,26 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ディープシーカーの左腕の希石</t>
+    <rPh sb="9" eb="11">
+      <t>ヒダリウデ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ディープシーカーの右腕の希石</t>
+    <rPh sb="9" eb="10">
+      <t>ミギ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -8612,7 +8632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B199"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -10209,6 +10229,22 @@
       </c>
       <c r="B199" s="3" t="s">
         <v>516</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A200" s="3">
+        <v>11217</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A201" s="3">
+        <v>11218</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABAC851-D4DB-4593-8D92-718927A37A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E35682-788D-4B16-8EC2-A9B716AF3B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -9873,7 +9873,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="3">
-        <v>9727</v>
+        <v>9827</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>390</v>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E35682-788D-4B16-8EC2-A9B716AF3B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF135226-CB83-4844-8D0B-9F5802345B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
     <sheet name="素材名と図鑑番号の対応" sheetId="2" r:id="rId2"/>
-    <sheet name="お知らせ" sheetId="3" r:id="rId3"/>
+    <sheet name="メンテ期間" sheetId="4" r:id="rId3"/>
+    <sheet name="お知らせ" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="522">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5666,13 +5667,35 @@
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>番号</t>
+    <rPh sb="0" eb="2">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>開始</t>
+    <rPh sb="0" eb="2">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>終了</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="181" formatCode="yyyy/m/d\ h:mm;@"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -6343,7 +6366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6415,6 +6438,12 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -10257,6 +10286,42 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA087EF-D4CB-4508-81E0-4C5741605FD2}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="15.58203125" style="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23">
+        <v>46268.916666666664</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46269</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FCBD9B-5783-443C-87DE-4B13994EA8C3}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF135226-CB83-4844-8D0B-9F5802345B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CF3C87-BDB4-4505-AF5F-427DED85BC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
     <sheet name="素材名と図鑑番号の対応" sheetId="2" r:id="rId2"/>
-    <sheet name="メンテ期間" sheetId="4" r:id="rId3"/>
-    <sheet name="お知らせ" sheetId="3" r:id="rId4"/>
+    <sheet name="お知らせ" sheetId="3" r:id="rId3"/>
+    <sheet name="メンテ期間" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10286,42 +10286,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA087EF-D4CB-4508-81E0-4C5741605FD2}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="2" max="3" width="15.58203125" style="23" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>519</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>520</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="23">
-        <v>46268.916666666664</v>
-      </c>
-      <c r="C2" s="23">
-        <v>46269</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FCBD9B-5783-443C-87DE-4B13994EA8C3}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -10357,4 +10321,40 @@
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA087EF-D4CB-4508-81E0-4C5741605FD2}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="15.58203125" style="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23">
+        <v>46268.916666666664</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46269</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CF3C87-BDB4-4505-AF5F-427DED85BC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F731D2-0626-4521-839B-7CA5A2111091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -5695,7 +5695,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="181" formatCode="yyyy/m/d\ h:mm;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy/m/d\ h:mm;@"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -6366,7 +6366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6439,10 +6439,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10335,10 +10332,10 @@
       <c r="A1" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" t="s">
         <v>520</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" t="s">
         <v>521</v>
       </c>
     </row>
@@ -10348,9 +10345,6 @@
       </c>
       <c r="B2" s="23">
         <v>46268.916666666664</v>
-      </c>
-      <c r="C2" s="23">
-        <v>46269</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F731D2-0626-4521-839B-7CA5A2111091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECAF02B-1A9D-4839-B420-6AD361E9BD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="523">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5685,6 +5685,13 @@
     <t>終了</t>
     <rPh sb="0" eb="2">
       <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>未定</t>
+    <rPh sb="0" eb="2">
+      <t>ミテイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -10343,8 +10350,11 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="23">
-        <v>46268.916666666664</v>
+      <c r="B2" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECAF02B-1A9D-4839-B420-6AD361E9BD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F718BC5-EA18-4EFB-B5EC-38459F7C96A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -3464,103 +3464,6 @@
   </si>
   <si>
     <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4(※2))</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>※1極キングルビードラゴン、極キングサファイアドラゴン、極エメラルドドラゴンは確定で各2体ドロップする。極キングゴールドドラゴン、極キングメタルドラゴンはいずれか一方がドロップし、それが2回続く。(何属性が落ちるかは1Fと6Fで出たモンスターの属性を見ればわかります。)(※1の説明を報酬リストに組み込むとややこしくなるため簡潔な表記にしています。),※2表記した数は最大値です。乱入が3Fのとき属性軽減たまドラが1体、6Fのとき極キング○○○ドラゴンが4体、9Fで創装の宝玉らのランダムドロップが1体減少する。(属性軽減たまドラは不確定ドロップであるため、ドロップ数が0になることもある。)</t>
-    <rPh sb="2" eb="3">
-      <t>ゴク</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ゴク</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ゴク</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>ゴク</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>ゴク</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>イッポウ</t>
-    </rPh>
-    <rPh sb="94" eb="95">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="95" eb="96">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="99" eb="102">
-      <t>ナニゾクセイ</t>
-    </rPh>
-    <rPh sb="103" eb="104">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="114" eb="115">
-      <t>デ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ゾクセイ</t>
-    </rPh>
-    <rPh sb="125" eb="126">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="139" eb="141">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="142" eb="144">
-      <t>ホウシュウ</t>
-    </rPh>
-    <rPh sb="148" eb="149">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="150" eb="151">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="162" eb="164">
-      <t>カンケツ</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>ヒョウキ</t>
-    </rPh>
-    <rPh sb="178" eb="180">
-      <t>ヒョウキ</t>
-    </rPh>
-    <rPh sb="182" eb="183">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="184" eb="187">
-      <t>サイダイチ</t>
-    </rPh>
-    <rPh sb="190" eb="192">
-      <t>ランニュウ</t>
-    </rPh>
-    <rPh sb="198" eb="200">
-      <t>ゾクセイ</t>
-    </rPh>
-    <rPh sb="200" eb="202">
-      <t>ケイゲン</t>
-    </rPh>
-    <rPh sb="208" eb="209">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="215" eb="216">
-      <t>ゴク</t>
-    </rPh>
-    <rPh sb="228" eb="229">
-      <t>タイ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -5693,6 +5596,14 @@
     <rPh sb="0" eb="2">
       <t>ミテイ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>※1極キング系について、ルビードラ・サファイアドラ・エメラルドドラは各2体確定。
+ゴールドドラ・メタルドラは1Fと6Fで出現した属性のものが計2体ドロップします。 
+※2記載数は最大値です。乱入階層により一部ドロップが減少します
+（3F：属性軽減たまドラ -1体、6F：極キング系 -4体、9F：宝玉などのランダム枠 -1体）。
+※3属性軽減たまドラは元が不確定のため0体になる場合もあります。</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -6373,7 +6284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6448,6 +6359,9 @@
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -7053,7 +6967,7 @@
         <v>26</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>19</v>
@@ -7319,7 +7233,7 @@
         <v>192</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q9" s="12" t="s">
         <v>193</v>
@@ -7533,7 +7447,7 @@
       </c>
       <c r="Q13" s="13"/>
       <c r="R13" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
@@ -7581,7 +7495,7 @@
         <v>276</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q14" s="13"/>
       <c r="R14" s="12" t="s">
@@ -7635,7 +7549,7 @@
         <v>289</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="12" t="s">
@@ -7684,10 +7598,10 @@
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q16" s="12" t="s">
         <v>300</v>
@@ -7697,7 +7611,7 @@
       </c>
       <c r="S16" s="13"/>
       <c r="T16" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7729,10 +7643,10 @@
         <v>252</v>
       </c>
       <c r="J17" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="K17" s="9" t="s">
         <v>311</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>312</v>
       </c>
       <c r="L17" s="11">
         <v>7777</v>
@@ -7754,16 +7668,16 @@
       <c r="S17" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="T17" s="12" t="s">
-        <v>310</v>
+      <c r="T17" s="24" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="18" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>327</v>
       </c>
       <c r="C18" s="9">
         <v>99</v>
@@ -7772,19 +7686,19 @@
         <v>16</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>328</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>329</v>
       </c>
       <c r="L18" s="11">
         <v>2970</v>
@@ -7792,24 +7706,24 @@
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
       <c r="O18" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="P18" s="12" t="s">
         <v>372</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>373</v>
       </c>
       <c r="Q18" s="13"/>
       <c r="R18" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S18" s="13"/>
       <c r="T18" s="13"/>
     </row>
     <row r="19" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C19" s="9">
         <v>99</v>
@@ -7818,42 +7732,42 @@
         <v>16</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K19" s="9" t="s">
         <v>334</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>335</v>
       </c>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="O19" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="P19" s="12" t="s">
         <v>381</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>382</v>
       </c>
       <c r="Q19" s="13"/>
       <c r="R19" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
     </row>
     <row r="20" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C20" s="9">
         <v>99</v>
@@ -7862,42 +7776,42 @@
         <v>15</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="K20" s="9" t="s">
         <v>338</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>339</v>
       </c>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
       <c r="O20" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="P20" s="12" t="s">
         <v>386</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>387</v>
       </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="S20" s="13"/>
       <c r="T20" s="13"/>
     </row>
     <row r="21" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C21" s="9">
         <v>99</v>
@@ -7908,15 +7822,15 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>342</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>343</v>
       </c>
       <c r="L21" s="11">
         <v>2970</v>
@@ -7924,24 +7838,24 @@
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
       <c r="O21" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="P21" s="12" t="s">
         <v>391</v>
-      </c>
-      <c r="P21" s="12" t="s">
-        <v>392</v>
       </c>
       <c r="Q21" s="13"/>
       <c r="R21" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="S21" s="13"/>
       <c r="T21" s="13"/>
     </row>
     <row r="22" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C22" s="9">
         <v>99</v>
@@ -7951,20 +7865,20 @@
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G22" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>345</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>346</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>348</v>
       </c>
       <c r="L22" s="11">
         <v>2970</v>
@@ -7972,22 +7886,22 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="S22" s="13"/>
       <c r="T22" s="13"/>
     </row>
     <row r="23" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C23" s="9">
         <v>99</v>
@@ -7996,21 +7910,21 @@
         <v>15</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="K23" s="9" t="s">
         <v>350</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>351</v>
       </c>
       <c r="L23" s="11">
         <v>2970</v>
@@ -8018,24 +7932,24 @@
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
       <c r="O23" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="S23" s="12" t="s">
         <v>427</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>428</v>
       </c>
       <c r="T23" s="13"/>
     </row>
     <row r="24" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C24" s="9">
         <v>99</v>
@@ -8044,19 +7958,19 @@
         <v>16</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L24" s="11">
         <v>2970</v>
@@ -8064,22 +7978,22 @@
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
       <c r="O24" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S24" s="13"/>
       <c r="T24" s="13"/>
     </row>
     <row r="25" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C25" s="9">
         <v>99</v>
@@ -8088,19 +8002,19 @@
         <v>16</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L25" s="11">
         <v>2970</v>
@@ -8108,24 +8022,24 @@
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Q25" s="13"/>
       <c r="R25" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="S25" s="13"/>
       <c r="T25" s="13"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C26" s="9">
         <v>99</v>
@@ -8134,19 +8048,19 @@
         <v>15</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L26" s="11">
         <v>2970</v>
@@ -8154,24 +8068,24 @@
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
       <c r="O26" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q26" s="13"/>
       <c r="R26" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S26" s="13"/>
       <c r="T26" s="13"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C27" s="9">
         <v>99</v>
@@ -8182,15 +8096,15 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="K27" s="9" t="s">
         <v>361</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>362</v>
       </c>
       <c r="L27" s="11">
         <v>2970</v>
@@ -8198,24 +8112,24 @@
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
       <c r="O27" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q27" s="13"/>
       <c r="R27" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
     </row>
     <row r="28" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C28" s="9">
         <v>99</v>
@@ -8225,45 +8139,45 @@
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G28" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>345</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>346</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>365</v>
       </c>
       <c r="L28" s="11">
         <v>2970</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N28" s="9"/>
       <c r="O28" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="S28" s="13"/>
       <c r="T28" s="13"/>
     </row>
     <row r="29" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C29" s="9">
         <v>99</v>
@@ -8272,48 +8186,48 @@
         <v>15</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L29" s="11">
         <v>7777</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N29" s="9"/>
       <c r="O29" s="12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="T29" s="13"/>
     </row>
     <row r="30" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>442</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>443</v>
       </c>
       <c r="C30" s="9">
         <v>99</v>
@@ -8323,47 +8237,47 @@
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>453</v>
-      </c>
       <c r="K30" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L30" s="9"/>
       <c r="M30" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N30" s="9"/>
       <c r="O30" s="12" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P30" s="13"/>
       <c r="Q30" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="R30" s="13"/>
       <c r="S30" s="12" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C31" s="9">
         <v>99</v>
@@ -8373,47 +8287,47 @@
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="9"/>
       <c r="J31" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L31" s="9"/>
       <c r="M31" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N31" s="9"/>
       <c r="O31" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P31" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="P31" s="12" t="s">
+      <c r="Q31" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="Q31" s="12" t="s">
+      <c r="R31" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="R31" s="12" t="s">
+      <c r="S31" s="12" t="s">
         <v>487</v>
-      </c>
-      <c r="S31" s="12" t="s">
-        <v>488</v>
       </c>
       <c r="T31" s="13"/>
     </row>
     <row r="32" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C32" s="9">
         <v>99</v>
@@ -8422,48 +8336,48 @@
         <v>15</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J32" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="K32" s="9" t="s">
         <v>454</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>455</v>
       </c>
       <c r="L32" s="9"/>
       <c r="M32" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="N32" s="9" t="s">
         <v>457</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>458</v>
       </c>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C33" s="9">
         <v>99</v>
@@ -8473,20 +8387,20 @@
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="K33" s="9" t="s">
         <v>461</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>462</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
@@ -8494,26 +8408,26 @@
         <v>30</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="R33" s="13"/>
       <c r="S33" s="12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="34" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C34" s="9">
         <v>99</v>
@@ -8522,42 +8436,42 @@
         <v>15</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
       <c r="O34" s="12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="P34" s="13"/>
       <c r="Q34" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="R34" s="13"/>
       <c r="S34" s="13"/>
       <c r="T34" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C35" s="9">
         <v>99</v>
@@ -8566,50 +8480,50 @@
         <v>15</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F35" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="H35" s="10" t="s">
+      <c r="I35" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="K35" s="9" t="s">
         <v>470</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>471</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
       <c r="S35" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T35" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C36" s="9">
         <v>99</v>
@@ -8618,23 +8532,23 @@
         <v>15</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F36" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="G36" s="10" t="s">
         <v>472</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>473</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J36" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>474</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>475</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
@@ -8642,18 +8556,18 @@
         <v>30</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R36" s="13"/>
       <c r="S36" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T36" s="12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -9157,7 +9071,7 @@
         <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9165,7 +9079,7 @@
         <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9173,7 +9087,7 @@
         <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9181,7 +9095,7 @@
         <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9189,7 +9103,7 @@
         <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9821,7 +9735,7 @@
         <v>8914</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9829,7 +9743,7 @@
         <v>8916</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9837,7 +9751,7 @@
         <v>7680</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9845,7 +9759,7 @@
         <v>7681</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9853,7 +9767,7 @@
         <v>7684</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9861,7 +9775,7 @@
         <v>7686</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9869,7 +9783,7 @@
         <v>9227</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9877,7 +9791,7 @@
         <v>9229</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9885,7 +9799,7 @@
         <v>9455</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9893,7 +9807,7 @@
         <v>9457</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9901,7 +9815,7 @@
         <v>9716</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9909,7 +9823,7 @@
         <v>9827</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9917,7 +9831,7 @@
         <v>322</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9925,7 +9839,7 @@
         <v>323</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9933,7 +9847,7 @@
         <v>324</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9941,7 +9855,7 @@
         <v>325</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9949,7 +9863,7 @@
         <v>1109</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9957,7 +9871,7 @@
         <v>326</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9965,7 +9879,7 @@
         <v>327</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9973,7 +9887,7 @@
         <v>328</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9981,7 +9895,7 @@
         <v>329</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9989,7 +9903,7 @@
         <v>1095</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9997,7 +9911,7 @@
         <v>330</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10005,7 +9919,7 @@
         <v>331</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10013,7 +9927,7 @@
         <v>332</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10021,7 +9935,7 @@
         <v>333</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10029,7 +9943,7 @@
         <v>1096</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10037,7 +9951,7 @@
         <v>334</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10045,7 +9959,7 @@
         <v>335</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10053,7 +9967,7 @@
         <v>336</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10061,7 +9975,7 @@
         <v>337</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10069,7 +9983,7 @@
         <v>1110</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10077,7 +9991,7 @@
         <v>338</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10085,7 +9999,7 @@
         <v>339</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10093,7 +10007,7 @@
         <v>340</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10101,7 +10015,7 @@
         <v>341</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10109,7 +10023,7 @@
         <v>1111</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10117,7 +10031,7 @@
         <v>11046</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10125,7 +10039,7 @@
         <v>11039</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10133,7 +10047,7 @@
         <v>11040</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10141,7 +10055,7 @@
         <v>11037</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10149,7 +10063,7 @@
         <v>11038</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10157,7 +10071,7 @@
         <v>1340</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10165,7 +10079,7 @@
         <v>13047</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10173,7 +10087,7 @@
         <v>13048</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10181,7 +10095,7 @@
         <v>3826</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10189,7 +10103,7 @@
         <v>1325</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10197,7 +10111,7 @@
         <v>1326</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10205,7 +10119,7 @@
         <v>1327</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10213,7 +10127,7 @@
         <v>1328</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10221,7 +10135,7 @@
         <v>1329</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10229,7 +10143,7 @@
         <v>13303</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10237,7 +10151,7 @@
         <v>13304</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10245,7 +10159,7 @@
         <v>12345</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10253,7 +10167,7 @@
         <v>12346</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10261,7 +10175,7 @@
         <v>12114</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10269,7 +10183,7 @@
         <v>11217</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10277,7 +10191,7 @@
         <v>11218</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -10337,13 +10251,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B1" t="s">
         <v>519</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>520</v>
-      </c>
-      <c r="C1" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -10351,10 +10265,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F718BC5-EA18-4EFB-B5EC-38459F7C96A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BF3F08-6944-43A3-A588-15858394212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -5599,11 +5599,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>※1極キング系について、ルビードラ・サファイアドラ・エメラルドドラは各2体確定。
-ゴールドドラ・メタルドラは1Fと6Fで出現した属性のものが計2体ドロップします。 
-※2記載数は最大値です。乱入階層により一部ドロップが減少します
-（3F：属性軽減たまドラ -1体、6F：極キング系 -4体、9F：宝玉などのランダム枠 -1体）。
-※3属性軽減たまドラは元が不確定のため0体になる場合もあります。</t>
+    <t>※1極キング系について、ルビードラ・サファイアドラ・エメラルドドラは各2体確定。ゴールドドラ・メタルドラは1Fと6Fで出現した属性のものが計2体ドロップします。 ※2記載数は最大値です。乱入階層により一部ドロップが減少します（3F：属性軽減たまドラ -1体、6F：極キング系 -4体、9F：宝玉などのランダム枠 -1体）。※3属性軽減たまドラは元が不確定のため0体になる場合もあります。</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BF3F08-6944-43A3-A588-15858394212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D07EDD4-B13C-443F-AFBD-27F6A0681BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -5599,7 +5599,8 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>※1極キング系について、ルビードラ・サファイアドラ・エメラルドドラは各2体確定。ゴールドドラ・メタルドラは1Fと6Fで出現した属性のものが計2体ドロップします。 ※2記載数は最大値です。乱入階層により一部ドロップが減少します（3F：属性軽減たまドラ -1体、6F：極キング系 -4体、9F：宝玉などのランダム枠 -1体）。※3属性軽減たまドラは元が不確定のため0体になる場合もあります。</t>
+    <t>※1極キング系について、ルビードラ・サファイアドラ・エメラルドドラは各2体確定。ゴールドドラ・メタルドラは1Fと6Fで出現した属性のものが計2体ドロップします。 ※2記載数は最大値です。乱入階層により一部ドロップが減少します。
+（3F：属性軽減たまドラ -1体、6F：極キング系 -4体、9F：宝玉などのランダム枠 -1体）※3属性軽減たまドラは元が不確定のため0体になる場合もあります。</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D07EDD4-B13C-443F-AFBD-27F6A0681BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158AE295-BBD4-45D8-879B-47F4A797DA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -3463,10 +3463,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4(※2))</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>1.5億</t>
     <rPh sb="3" eb="4">
       <t>オク</t>
@@ -5601,6 +5597,10 @@
   <si>
     <t>※1極キング系について、ルビードラ・サファイアドラ・エメラルドドラは各2体確定。ゴールドドラ・メタルドラは1Fと6Fで出現した属性のものが計2体ドロップします。 ※2記載数は最大値です。乱入階層により一部ドロップが減少します。
 （3F：属性軽減たまドラ -1体、6F：極キング系 -4体、9F：宝玉などのランダム枠 -1体）※3属性軽減たまドラは元が不確定のため0体になる場合もあります。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4(※2)(※3))</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -6964,7 +6964,7 @@
         <v>26</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>19</v>
@@ -7230,7 +7230,7 @@
         <v>192</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q9" s="12" t="s">
         <v>193</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="Q13" s="13"/>
       <c r="R13" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
@@ -7492,7 +7492,7 @@
         <v>276</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q14" s="13"/>
       <c r="R14" s="12" t="s">
@@ -7546,7 +7546,7 @@
         <v>289</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="12" t="s">
@@ -7595,10 +7595,10 @@
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q16" s="12" t="s">
         <v>300</v>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="S16" s="13"/>
       <c r="T16" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7640,10 +7640,10 @@
         <v>252</v>
       </c>
       <c r="J17" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="K17" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>311</v>
       </c>
       <c r="L17" s="11">
         <v>7777</v>
@@ -7663,18 +7663,18 @@
         <v>308</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>309</v>
+        <v>522</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="C18" s="9">
         <v>99</v>
@@ -7683,19 +7683,19 @@
         <v>16</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>328</v>
       </c>
       <c r="L18" s="11">
         <v>2970</v>
@@ -7703,24 +7703,24 @@
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
       <c r="O18" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="P18" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>372</v>
       </c>
       <c r="Q18" s="13"/>
       <c r="R18" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="S18" s="13"/>
       <c r="T18" s="13"/>
     </row>
     <row r="19" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C19" s="9">
         <v>99</v>
@@ -7729,42 +7729,42 @@
         <v>16</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="K19" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>334</v>
       </c>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="O19" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="P19" s="12" t="s">
         <v>380</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>381</v>
       </c>
       <c r="Q19" s="13"/>
       <c r="R19" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
     </row>
     <row r="20" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C20" s="9">
         <v>99</v>
@@ -7773,42 +7773,42 @@
         <v>15</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="K20" s="9" t="s">
         <v>337</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>338</v>
       </c>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
       <c r="O20" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="P20" s="12" t="s">
         <v>385</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>386</v>
       </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="S20" s="13"/>
       <c r="T20" s="13"/>
     </row>
     <row r="21" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C21" s="9">
         <v>99</v>
@@ -7819,15 +7819,15 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>341</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>342</v>
       </c>
       <c r="L21" s="11">
         <v>2970</v>
@@ -7835,24 +7835,24 @@
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
       <c r="O21" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="P21" s="12" t="s">
         <v>390</v>
-      </c>
-      <c r="P21" s="12" t="s">
-        <v>391</v>
       </c>
       <c r="Q21" s="13"/>
       <c r="R21" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="S21" s="13"/>
       <c r="T21" s="13"/>
     </row>
     <row r="22" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C22" s="9">
         <v>99</v>
@@ -7862,20 +7862,20 @@
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G22" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>344</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>345</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>346</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>347</v>
       </c>
       <c r="L22" s="11">
         <v>2970</v>
@@ -7883,22 +7883,22 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="S22" s="13"/>
       <c r="T22" s="13"/>
     </row>
     <row r="23" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C23" s="9">
         <v>99</v>
@@ -7907,21 +7907,21 @@
         <v>15</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="K23" s="9" t="s">
         <v>349</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>350</v>
       </c>
       <c r="L23" s="11">
         <v>2970</v>
@@ -7929,24 +7929,24 @@
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
       <c r="O23" s="12" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="S23" s="12" t="s">
         <v>426</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>427</v>
       </c>
       <c r="T23" s="13"/>
     </row>
     <row r="24" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C24" s="9">
         <v>99</v>
@@ -7955,19 +7955,19 @@
         <v>16</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L24" s="11">
         <v>2970</v>
@@ -7975,22 +7975,22 @@
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
       <c r="O24" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S24" s="13"/>
       <c r="T24" s="13"/>
     </row>
     <row r="25" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C25" s="9">
         <v>99</v>
@@ -7999,19 +7999,19 @@
         <v>16</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L25" s="11">
         <v>2970</v>
@@ -8019,24 +8019,24 @@
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q25" s="13"/>
       <c r="R25" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S25" s="13"/>
       <c r="T25" s="13"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C26" s="9">
         <v>99</v>
@@ -8045,19 +8045,19 @@
         <v>15</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L26" s="11">
         <v>2970</v>
@@ -8065,24 +8065,24 @@
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
       <c r="O26" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q26" s="13"/>
       <c r="R26" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="S26" s="13"/>
       <c r="T26" s="13"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C27" s="9">
         <v>99</v>
@@ -8093,15 +8093,15 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="K27" s="9" t="s">
         <v>360</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>361</v>
       </c>
       <c r="L27" s="11">
         <v>2970</v>
@@ -8109,24 +8109,24 @@
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
       <c r="O27" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q27" s="13"/>
       <c r="R27" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
     </row>
     <row r="28" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C28" s="9">
         <v>99</v>
@@ -8136,45 +8136,45 @@
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G28" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>344</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>345</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>363</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>364</v>
       </c>
       <c r="L28" s="11">
         <v>2970</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N28" s="9"/>
       <c r="O28" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S28" s="13"/>
       <c r="T28" s="13"/>
     </row>
     <row r="29" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C29" s="9">
         <v>99</v>
@@ -8183,48 +8183,48 @@
         <v>15</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L29" s="11">
         <v>7777</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N29" s="9"/>
       <c r="O29" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T29" s="13"/>
     </row>
     <row r="30" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>441</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>442</v>
       </c>
       <c r="C30" s="9">
         <v>99</v>
@@ -8234,47 +8234,47 @@
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>452</v>
-      </c>
       <c r="K30" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L30" s="9"/>
       <c r="M30" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N30" s="9"/>
       <c r="O30" s="12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P30" s="13"/>
       <c r="Q30" s="12" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="R30" s="13"/>
       <c r="S30" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C31" s="9">
         <v>99</v>
@@ -8284,47 +8284,47 @@
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="9"/>
       <c r="J31" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L31" s="9"/>
       <c r="M31" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N31" s="9"/>
       <c r="O31" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="P31" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="P31" s="12" t="s">
+      <c r="Q31" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="Q31" s="12" t="s">
+      <c r="R31" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="R31" s="12" t="s">
+      <c r="S31" s="12" t="s">
         <v>486</v>
-      </c>
-      <c r="S31" s="12" t="s">
-        <v>487</v>
       </c>
       <c r="T31" s="13"/>
     </row>
     <row r="32" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C32" s="9">
         <v>99</v>
@@ -8333,48 +8333,48 @@
         <v>15</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J32" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="K32" s="9" t="s">
         <v>453</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>454</v>
       </c>
       <c r="L32" s="9"/>
       <c r="M32" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="N32" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>457</v>
       </c>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="12" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C33" s="9">
         <v>99</v>
@@ -8384,20 +8384,20 @@
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="K33" s="9" t="s">
         <v>460</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>461</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
@@ -8405,26 +8405,26 @@
         <v>30</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="R33" s="13"/>
       <c r="S33" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="34" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C34" s="9">
         <v>99</v>
@@ -8433,42 +8433,42 @@
         <v>15</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
       <c r="O34" s="12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="P34" s="13"/>
       <c r="Q34" s="12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="R34" s="13"/>
       <c r="S34" s="13"/>
       <c r="T34" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="35" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C35" s="9">
         <v>99</v>
@@ -8477,50 +8477,50 @@
         <v>15</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F35" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="H35" s="10" t="s">
+      <c r="I35" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="K35" s="9" t="s">
         <v>469</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>470</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
       <c r="S35" s="12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="T35" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C36" s="9">
         <v>99</v>
@@ -8529,23 +8529,23 @@
         <v>15</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F36" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="G36" s="10" t="s">
         <v>471</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>472</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J36" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>473</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>474</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
@@ -8553,18 +8553,18 @@
         <v>30</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R36" s="13"/>
       <c r="S36" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T36" s="12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -9068,7 +9068,7 @@
         <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9076,7 +9076,7 @@
         <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9084,7 +9084,7 @@
         <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9092,7 +9092,7 @@
         <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9100,7 +9100,7 @@
         <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9732,7 +9732,7 @@
         <v>8914</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9740,7 +9740,7 @@
         <v>8916</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9748,7 +9748,7 @@
         <v>7680</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9756,7 +9756,7 @@
         <v>7681</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9764,7 +9764,7 @@
         <v>7684</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9772,7 +9772,7 @@
         <v>7686</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9780,7 +9780,7 @@
         <v>9227</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9788,7 +9788,7 @@
         <v>9229</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9796,7 +9796,7 @@
         <v>9455</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9804,7 +9804,7 @@
         <v>9457</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9812,7 +9812,7 @@
         <v>9716</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9820,7 +9820,7 @@
         <v>9827</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9828,7 +9828,7 @@
         <v>322</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9836,7 +9836,7 @@
         <v>323</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9844,7 +9844,7 @@
         <v>324</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9852,7 +9852,7 @@
         <v>325</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9860,7 +9860,7 @@
         <v>1109</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9868,7 +9868,7 @@
         <v>326</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9876,7 +9876,7 @@
         <v>327</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9884,7 +9884,7 @@
         <v>328</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9892,7 +9892,7 @@
         <v>329</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9900,7 +9900,7 @@
         <v>1095</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9908,7 +9908,7 @@
         <v>330</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9916,7 +9916,7 @@
         <v>331</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9924,7 +9924,7 @@
         <v>332</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9932,7 +9932,7 @@
         <v>333</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9940,7 +9940,7 @@
         <v>1096</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9948,7 +9948,7 @@
         <v>334</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9956,7 +9956,7 @@
         <v>335</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9964,7 +9964,7 @@
         <v>336</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9972,7 +9972,7 @@
         <v>337</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9980,7 +9980,7 @@
         <v>1110</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9988,7 +9988,7 @@
         <v>338</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9996,7 +9996,7 @@
         <v>339</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10004,7 +10004,7 @@
         <v>340</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10012,7 +10012,7 @@
         <v>341</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10020,7 +10020,7 @@
         <v>1111</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10028,7 +10028,7 @@
         <v>11046</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10036,7 +10036,7 @@
         <v>11039</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10044,7 +10044,7 @@
         <v>11040</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10052,7 +10052,7 @@
         <v>11037</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10060,7 +10060,7 @@
         <v>11038</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10068,7 +10068,7 @@
         <v>1340</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10076,7 +10076,7 @@
         <v>13047</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10084,7 +10084,7 @@
         <v>13048</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10092,7 +10092,7 @@
         <v>3826</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10100,7 +10100,7 @@
         <v>1325</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10108,7 +10108,7 @@
         <v>1326</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10116,7 +10116,7 @@
         <v>1327</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10124,7 +10124,7 @@
         <v>1328</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10132,7 +10132,7 @@
         <v>1329</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10140,7 +10140,7 @@
         <v>13303</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10148,7 +10148,7 @@
         <v>13304</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10156,7 +10156,7 @@
         <v>12345</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10164,7 +10164,7 @@
         <v>12346</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10172,7 +10172,7 @@
         <v>12114</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10180,7 +10180,7 @@
         <v>11217</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10188,7 +10188,7 @@
         <v>11218</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -10248,13 +10248,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B1" t="s">
         <v>518</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>519</v>
-      </c>
-      <c r="C1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -10262,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
